--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2287,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K104"/>
+  <dimension ref="A1:K105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2350,84 +2350,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -2442,106 +2442,106 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2556,54 +2556,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2623,44 +2623,44 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2680,44 +2680,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2737,19 +2737,19 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2794,44 +2794,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2851,19 +2851,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2908,44 +2908,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2955,49 +2955,49 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3012,49 +3012,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3091,27 +3091,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3148,27 +3148,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3183,49 +3183,49 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3240,49 +3240,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3319,27 +3319,27 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3376,32 +3376,32 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3421,19 +3421,19 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3478,44 +3478,44 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3535,39 +3535,39 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3604,7 +3604,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3619,7 +3619,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3696,44 +3696,44 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3775,27 +3775,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3815,49 +3815,49 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3867,44 +3867,44 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3946,32 +3946,32 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3981,29 +3981,29 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4048,44 +4048,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4095,29 +4095,29 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4162,44 +4162,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4219,19 +4219,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4276,44 +4276,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,39 +4333,39 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4402,12 +4402,12 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4447,39 +4447,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4489,12 +4489,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4504,39 +4504,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4561,44 +4561,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4618,39 +4618,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4665,49 +4665,49 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4722,49 +4722,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4779,86 +4779,86 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4903,39 +4903,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4945,59 +4945,59 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5017,44 +5017,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5064,29 +5064,29 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5131,19 +5131,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5188,44 +5188,44 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5235,54 +5235,54 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5302,39 +5302,39 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5359,34 +5359,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5428,27 +5428,27 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5485,32 +5485,32 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5520,44 +5520,44 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5599,22 +5599,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5656,22 +5656,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5713,32 +5713,32 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5758,39 +5758,39 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5815,34 +5815,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5862,49 +5862,49 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5941,32 +5941,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5976,44 +5976,44 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6055,27 +6055,27 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6090,54 +6090,54 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6157,44 +6157,44 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6214,44 +6214,44 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6271,39 +6271,39 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6313,116 +6313,116 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6432,49 +6432,49 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -6489,49 +6489,49 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6568,27 +6568,27 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6603,54 +6603,54 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6660,54 +6660,54 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6717,49 +6717,49 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6774,49 +6774,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6853,32 +6853,32 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6898,39 +6898,39 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6955,39 +6955,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7012,44 +7012,44 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7069,19 +7069,19 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -7091,17 +7091,17 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7126,44 +7126,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7195,27 +7195,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7252,27 +7252,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7309,32 +7309,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7344,49 +7344,49 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7401,54 +7401,54 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7458,49 +7458,49 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7515,49 +7515,49 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7594,27 +7594,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7651,32 +7651,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7686,49 +7686,49 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7743,49 +7743,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7800,7 +7800,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -7822,32 +7822,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -7857,54 +7857,54 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7936,32 +7936,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7993,32 +7993,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8050,12 +8050,12 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -8065,17 +8065,17 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8107,27 +8107,27 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8164,55 +8164,112 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B104" t="inlineStr">
+      <c r="B105" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
+      <c r="C105" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D104" t="inlineStr">
+      <c r="D105" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E104" t="inlineStr">
+      <c r="E105" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F104" t="inlineStr">
+      <c r="F105" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
+      <c r="I105" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J104" t="inlineStr">
+      <c r="J105" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr">
+      <c r="K105" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2287,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2350,32 +2350,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2395,96 +2395,96 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2499,106 +2499,106 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -2613,54 +2613,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2680,44 +2680,44 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2737,44 +2737,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2794,19 +2794,19 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2851,44 +2851,44 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2908,19 +2908,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2965,44 +2965,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3012,49 +3012,49 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -3069,49 +3069,49 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3148,27 +3148,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3205,27 +3205,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3240,49 +3240,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3297,49 +3297,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3376,27 +3376,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3433,32 +3433,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -3468,7 +3468,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3478,19 +3478,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3535,44 +3535,44 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3592,39 +3592,39 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3661,7 +3661,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3706,39 +3706,39 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3753,44 +3753,44 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3832,27 +3832,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3872,49 +3872,49 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3924,44 +3924,44 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4003,32 +4003,32 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4038,29 +4038,29 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4095,7 +4095,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4105,44 +4105,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4152,29 +4152,29 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4219,44 +4219,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4276,19 +4276,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,44 +4333,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4390,39 +4390,39 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4459,12 +4459,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4504,39 +4504,39 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4561,39 +4561,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4618,44 +4618,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4675,39 +4675,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4722,49 +4722,49 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4779,49 +4779,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4836,86 +4836,86 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -4950,7 +4950,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -4960,39 +4960,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5002,59 +5002,59 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5064,7 +5064,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5074,44 +5074,44 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,29 +5121,29 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5188,19 +5188,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5245,44 +5245,44 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5292,54 +5292,54 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5359,39 +5359,39 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5416,34 +5416,34 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5485,27 +5485,27 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5542,32 +5542,32 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5577,44 +5577,44 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5656,22 +5656,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5713,22 +5713,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5770,32 +5770,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5815,39 +5815,39 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5872,34 +5872,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5919,49 +5919,49 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5998,32 +5998,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6033,44 +6033,44 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6112,27 +6112,27 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6147,54 +6147,54 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6214,44 +6214,44 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6271,44 +6271,44 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6328,39 +6328,39 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6370,116 +6370,116 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6489,49 +6489,49 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6546,49 +6546,49 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6603,7 +6603,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6625,27 +6625,27 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6660,54 +6660,54 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6717,54 +6717,54 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6774,49 +6774,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6831,49 +6831,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -6910,32 +6910,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6955,39 +6955,39 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7012,39 +7012,39 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7069,44 +7069,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7126,19 +7126,19 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -7148,17 +7148,17 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7183,44 +7183,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7252,27 +7252,27 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7309,27 +7309,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7366,32 +7366,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7401,49 +7401,49 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7458,54 +7458,54 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7515,49 +7515,49 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7572,49 +7572,49 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7651,27 +7651,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7708,32 +7708,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7743,49 +7743,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7800,49 +7800,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7879,32 +7879,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -7914,54 +7914,54 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -7993,32 +7993,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8050,32 +8050,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8107,12 +8107,12 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -8122,17 +8122,17 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8164,27 +8164,27 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8221,55 +8221,112 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -9659,7 +9659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:K103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9722,32 +9722,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -9755,46 +9755,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -9804,7 +9800,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -9812,7 +9808,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -9820,19 +9820,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -9842,22 +9842,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -9868,92 +9868,92 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -9963,60 +9963,60 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10024,31 +10024,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10058,27 +10054,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -10093,52 +10089,56 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I9" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10146,34 +10146,34 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10183,7 +10183,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -10191,11 +10191,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10203,19 +10199,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10225,12 +10221,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10240,7 +10236,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -10260,44 +10256,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -10305,27 +10301,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -10335,12 +10335,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10350,35 +10350,35 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10403,103 +10403,103 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10509,35 +10509,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10547,22 +10547,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -10578,34 +10578,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10623,56 +10623,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -10680,42 +10676,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -10733,56 +10733,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10790,7 +10786,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10798,19 +10798,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -10820,27 +10820,27 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
@@ -10851,19 +10851,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10888,50 +10888,50 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10941,7 +10941,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -10949,31 +10949,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -10983,27 +10979,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -11018,34 +11014,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11055,15 +11051,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I26" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11071,19 +11071,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11093,22 +11093,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11124,34 +11124,34 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11161,7 +11161,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11169,11 +11169,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11181,44 +11177,44 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -11226,42 +11222,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11271,35 +11271,35 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11309,12 +11309,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11324,12 +11324,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
@@ -11340,44 +11340,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -11385,11 +11385,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11397,52 +11393,56 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11450,19 +11450,19 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11472,12 +11472,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11487,7 +11487,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -11503,19 +11503,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11525,50 +11525,50 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11578,22 +11578,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11609,44 +11609,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -11662,34 +11662,34 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -11710,24 +11710,24 @@
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -11737,12 +11737,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -11752,12 +11752,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -11768,19 +11768,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11790,50 +11790,50 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11843,12 +11843,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -11858,7 +11858,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -11869,24 +11869,24 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -11922,39 +11922,39 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -11972,31 +11972,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12006,12 +12002,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12021,7 +12017,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12053,7 +12049,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12063,12 +12059,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12078,7 +12074,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12110,7 +12106,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12120,12 +12116,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12135,7 +12131,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12167,7 +12163,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12177,22 +12173,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -12212,52 +12208,56 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I48" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12265,19 +12265,19 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12287,12 +12287,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12302,7 +12302,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12318,19 +12318,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12340,50 +12340,50 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12393,12 +12393,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -12408,7 +12408,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -12424,34 +12424,34 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -12469,64 +12469,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I53" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12534,34 +12534,34 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -12571,7 +12571,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -12599,22 +12599,22 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -12632,11 +12632,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12656,22 +12652,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -12681,35 +12677,39 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -12719,12 +12719,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -12734,35 +12734,35 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12772,12 +12772,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -12787,35 +12787,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12825,22 +12825,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -12856,19 +12856,19 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -12909,34 +12909,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -12954,56 +12954,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -13011,7 +13007,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I62" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13019,34 +13019,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -13056,7 +13056,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -13067,96 +13067,92 @@
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -13166,7 +13162,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -13174,7 +13170,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13182,19 +13182,19 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13204,12 +13204,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -13219,12 +13219,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
@@ -13235,19 +13235,19 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13257,22 +13257,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -13288,19 +13288,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -13325,7 +13325,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -13336,96 +13336,92 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -13435,35 +13431,39 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13473,22 +13473,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -13499,24 +13499,24 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13526,12 +13526,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -13552,24 +13552,24 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13579,22 +13579,22 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -13610,44 +13610,44 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -13663,44 +13663,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -13708,31 +13708,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -13742,12 +13738,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -13757,7 +13753,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -13789,22 +13785,22 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13814,7 +13810,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -13822,27 +13818,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr"/>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -13852,12 +13852,12 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -13867,113 +13867,113 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -13981,31 +13981,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14015,12 +14011,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -14030,7 +14026,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -14062,32 +14058,32 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -14095,7 +14091,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14115,22 +14115,22 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -14140,7 +14140,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -14168,22 +14168,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -14193,19 +14193,15 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14225,7 +14221,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -14235,12 +14231,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -14250,7 +14246,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -14282,40 +14278,44 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14335,22 +14335,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -14368,11 +14368,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14392,32 +14388,32 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -14425,7 +14421,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14433,34 +14433,34 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -14470,7 +14470,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -14481,49 +14481,49 @@
       <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -14551,22 +14551,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -14604,32 +14604,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -14657,22 +14657,22 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -14682,39 +14682,35 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -14724,27 +14720,27 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -14771,32 +14767,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -14804,52 +14800,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -14877,32 +14877,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -14930,32 +14930,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -14983,32 +14983,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -15016,46 +15016,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -15065,7 +15061,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -15073,52 +15069,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -15146,55 +15146,108 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B102" t="inlineStr">
+      <c r="B103" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C102" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
+      <c r="D103" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E102" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F103" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr">
+      <c r="I103" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J102" t="inlineStr">
+      <c r="J103" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -9659,7 +9659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K103"/>
+  <dimension ref="A1:K104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9722,7 +9722,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -9732,12 +9732,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9763,44 +9763,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -9808,46 +9808,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -9857,7 +9853,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -9865,7 +9861,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -9873,19 +9873,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -9895,22 +9895,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -9921,92 +9921,92 @@
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10016,60 +10016,60 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -10077,31 +10077,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10111,27 +10107,27 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -10146,52 +10142,56 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10199,34 +10199,34 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -10244,11 +10244,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10256,19 +10252,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10278,12 +10274,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -10293,7 +10289,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -10313,44 +10309,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -10358,27 +10354,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10403,35 +10403,35 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10456,103 +10456,103 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10562,35 +10562,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10600,22 +10600,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -10631,34 +10631,34 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -10676,56 +10676,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -10733,42 +10729,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -10786,56 +10786,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -10843,7 +10839,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10851,19 +10851,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10873,27 +10873,27 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
@@ -10904,19 +10904,19 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -10941,50 +10941,50 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -10994,7 +10994,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -11002,31 +11002,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11036,27 +11032,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -11071,34 +11067,34 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11108,15 +11104,19 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11124,19 +11124,19 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11146,22 +11146,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11177,34 +11177,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11214,7 +11214,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -11222,11 +11222,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11234,44 +11230,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -11279,42 +11275,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11324,35 +11324,35 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -11362,12 +11362,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11377,12 +11377,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -11393,44 +11393,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -11438,11 +11438,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11450,52 +11446,56 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11503,19 +11503,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11525,12 +11525,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11540,7 +11540,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -11556,19 +11556,19 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -11578,50 +11578,50 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -11631,22 +11631,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -11662,44 +11662,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -11715,34 +11715,34 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -11763,24 +11763,24 @@
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -11790,12 +11790,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -11805,12 +11805,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
@@ -11821,19 +11821,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -11843,50 +11843,50 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -11896,12 +11896,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -11911,7 +11911,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -11922,24 +11922,24 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -11949,12 +11949,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11964,7 +11964,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -11975,39 +11975,39 @@
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12017,7 +12017,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12025,31 +12025,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12059,12 +12055,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12074,7 +12070,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12106,7 +12102,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12116,12 +12112,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12131,7 +12127,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12163,7 +12159,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12173,12 +12169,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12188,7 +12184,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -12220,7 +12216,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12230,22 +12226,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -12265,52 +12261,56 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12318,19 +12318,19 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12340,12 +12340,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12355,7 +12355,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -12371,19 +12371,19 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12393,50 +12393,50 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12446,12 +12446,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -12477,34 +12477,34 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -12522,64 +12522,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12587,34 +12587,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -12624,7 +12624,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -12652,22 +12652,22 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -12677,7 +12677,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -12685,11 +12685,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12709,22 +12705,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -12734,35 +12730,39 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -12772,12 +12772,12 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -12787,35 +12787,35 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -12840,35 +12840,35 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12878,22 +12878,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -12909,19 +12909,19 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12931,12 +12931,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -12962,34 +12962,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -13007,56 +13007,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -13064,7 +13060,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13072,34 +13072,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -13120,96 +13120,92 @@
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -13219,7 +13215,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -13227,7 +13223,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13235,19 +13235,19 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13257,12 +13257,12 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -13272,12 +13272,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -13288,19 +13288,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13310,22 +13310,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -13341,19 +13341,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13363,12 +13363,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -13378,7 +13378,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -13389,96 +13389,92 @@
       <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -13488,35 +13484,39 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13526,22 +13526,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -13552,24 +13552,24 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -13579,12 +13579,12 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -13605,24 +13605,24 @@
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -13632,22 +13632,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -13663,44 +13663,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -13716,44 +13716,44 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -13761,31 +13761,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -13795,12 +13791,12 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -13810,7 +13806,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -13842,22 +13838,22 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -13867,7 +13863,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -13875,27 +13871,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -13905,12 +13905,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -13920,113 +13920,113 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -14034,31 +14034,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -14068,12 +14064,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -14083,7 +14079,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -14115,32 +14111,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -14148,7 +14144,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14168,22 +14168,22 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -14221,22 +14221,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -14246,19 +14246,15 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14278,7 +14274,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -14288,12 +14284,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -14303,7 +14299,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -14335,40 +14331,44 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14388,22 +14388,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -14413,7 +14413,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -14421,11 +14421,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14445,32 +14441,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -14478,7 +14474,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14486,34 +14486,34 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -14523,7 +14523,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -14534,49 +14534,49 @@
       <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -14604,22 +14604,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -14629,7 +14629,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -14657,32 +14657,32 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -14710,22 +14710,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -14735,39 +14735,35 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -14777,27 +14773,27 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -14824,32 +14820,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -14857,52 +14853,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -14930,32 +14930,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -14983,32 +14983,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -15036,32 +15036,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -15069,46 +15069,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -15118,7 +15114,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -15126,52 +15122,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -15199,55 +15199,108 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B103" t="inlineStr">
+      <c r="B104" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
+      <c r="D104" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E103" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F104" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="G104" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
+      <c r="I104" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J103" t="inlineStr">
+      <c r="J104" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr">
+      <c r="K104" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2287,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2350,32 +2350,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2385,54 +2385,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -2452,96 +2452,96 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -2556,106 +2556,106 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2670,54 +2670,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2737,44 +2737,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2794,44 +2794,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2851,19 +2851,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2908,44 +2908,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2955,7 +2955,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2965,19 +2965,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3022,44 +3022,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3069,49 +3069,49 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3126,49 +3126,49 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3205,27 +3205,27 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3262,27 +3262,27 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3297,49 +3297,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3354,49 +3354,49 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3433,27 +3433,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3490,32 +3490,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3535,19 +3535,19 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3592,44 +3592,44 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3649,39 +3649,39 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3718,7 +3718,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3763,39 +3763,39 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3810,44 +3810,44 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3889,27 +3889,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -3929,49 +3929,49 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3981,44 +3981,44 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4060,32 +4060,32 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -4095,29 +4095,29 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -4162,44 +4162,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4209,29 +4209,29 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4246,7 +4246,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4276,44 +4276,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,19 +4333,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4380,7 +4380,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4390,44 +4390,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4447,39 +4447,39 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4516,12 +4516,12 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4561,39 +4561,39 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4603,12 +4603,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4618,39 +4618,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4675,44 +4675,44 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4732,39 +4732,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4779,49 +4779,49 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4836,49 +4836,49 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4893,86 +4893,86 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5017,39 +5017,39 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5059,59 +5059,59 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -5131,44 +5131,44 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5178,29 +5178,29 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5215,7 +5215,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5235,7 +5235,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5245,19 +5245,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5302,44 +5302,44 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5349,54 +5349,54 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5416,39 +5416,39 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5473,34 +5473,34 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5542,27 +5542,27 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5599,32 +5599,32 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5634,44 +5634,44 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5713,22 +5713,22 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5770,22 +5770,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -5805,7 +5805,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5827,32 +5827,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5872,39 +5872,39 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -5929,34 +5929,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5976,49 +5976,49 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6055,32 +6055,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6090,44 +6090,44 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6169,27 +6169,27 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6204,54 +6204,54 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6271,44 +6271,44 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6328,44 +6328,44 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6385,39 +6385,39 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6427,116 +6427,116 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6546,49 +6546,49 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6603,49 +6603,49 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6682,27 +6682,27 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -6717,54 +6717,54 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6774,54 +6774,54 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6831,49 +6831,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6888,49 +6888,49 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -6967,32 +6967,32 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7012,39 +7012,39 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7059,7 +7059,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7069,39 +7069,39 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7126,44 +7126,44 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7183,19 +7183,19 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -7205,17 +7205,17 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7240,44 +7240,44 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7309,27 +7309,27 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7366,27 +7366,27 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7423,32 +7423,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7458,49 +7458,49 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7515,54 +7515,54 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7572,49 +7572,49 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7629,49 +7629,49 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7708,27 +7708,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7765,32 +7765,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7800,49 +7800,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7857,49 +7857,49 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7936,32 +7936,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7971,54 +7971,54 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8050,32 +8050,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8107,32 +8107,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8164,12 +8164,12 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -8179,17 +8179,17 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8221,27 +8221,27 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8278,55 +8278,112 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2287,7 +2287,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K109"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2350,22 +2350,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2385,44 +2385,44 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2464,22 +2464,22 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2499,54 +2499,54 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2556,54 +2556,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2613,7 +2613,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2623,96 +2623,96 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -2727,106 +2727,106 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -2841,54 +2841,54 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2908,44 +2908,44 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -2965,44 +2965,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -3022,19 +3022,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3069,7 +3069,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3079,44 +3079,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3136,19 +3136,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3193,44 +3193,44 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -3240,49 +3240,49 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3297,49 +3297,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3354,7 +3354,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3376,27 +3376,27 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3411,7 +3411,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3433,27 +3433,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3468,49 +3468,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3525,49 +3525,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3604,27 +3604,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3661,32 +3661,32 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3706,19 +3706,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3763,44 +3763,44 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -3810,7 +3810,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3820,39 +3820,39 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3889,7 +3889,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -3934,39 +3934,39 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -3981,44 +3981,44 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4060,27 +4060,27 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -4100,49 +4100,49 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -4152,44 +4152,44 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4231,32 +4231,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -4266,29 +4266,29 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -4333,44 +4333,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -4380,29 +4380,29 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4417,7 +4417,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -4447,44 +4447,44 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4504,19 +4504,19 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4561,44 +4561,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4618,39 +4618,39 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4687,12 +4687,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4722,7 +4722,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4732,39 +4732,39 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -4774,12 +4774,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4789,39 +4789,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4831,12 +4831,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4846,44 +4846,44 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -4893,7 +4893,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4903,39 +4903,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -4950,49 +4950,49 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5007,49 +5007,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5064,86 +5064,86 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -5178,7 +5178,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -5188,39 +5188,39 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5230,59 +5230,59 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5292,7 +5292,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -5302,44 +5302,44 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5349,29 +5349,29 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -5416,19 +5416,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5463,7 +5463,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5473,44 +5473,44 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5520,54 +5520,54 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5587,39 +5587,39 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5644,34 +5644,34 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -5691,7 +5691,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5713,27 +5713,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5770,32 +5770,32 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -5805,44 +5805,44 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -5862,7 +5862,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5884,22 +5884,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -5941,22 +5941,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -5998,32 +5998,32 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -6033,7 +6033,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6043,39 +6043,39 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -6090,7 +6090,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6100,34 +6100,34 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6147,49 +6147,49 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6226,32 +6226,32 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -6261,44 +6261,44 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6318,7 +6318,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -6340,27 +6340,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6375,54 +6375,54 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -6442,44 +6442,44 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6489,7 +6489,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6499,44 +6499,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6556,39 +6556,39 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -6598,116 +6598,116 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6717,49 +6717,49 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6774,49 +6774,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6853,27 +6853,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6888,54 +6888,54 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -6945,54 +6945,54 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7002,49 +7002,49 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7059,49 +7059,49 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7116,7 +7116,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -7138,32 +7138,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7173,7 +7173,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7183,39 +7183,39 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7230,7 +7230,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7240,39 +7240,39 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7287,7 +7287,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7297,44 +7297,44 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7354,19 +7354,19 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -7376,17 +7376,17 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7401,7 +7401,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7411,44 +7411,44 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7480,27 +7480,27 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -7515,7 +7515,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7537,27 +7537,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7594,32 +7594,32 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7629,49 +7629,49 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7686,54 +7686,54 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -7743,49 +7743,49 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -7800,49 +7800,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7857,7 +7857,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -7879,27 +7879,27 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -7936,32 +7936,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -7971,49 +7971,49 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8028,49 +8028,49 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8107,32 +8107,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8142,54 +8142,54 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8199,7 +8199,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8221,32 +8221,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8278,32 +8278,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8313,7 +8313,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8335,12 +8335,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8350,17 +8350,17 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8392,27 +8392,27 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8449,55 +8449,112 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B109" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C109" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H109" t="inlineStr">
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J109" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -1649,7 +1649,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1707,17 +1707,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>17151</t>
+          <t>31091</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=88084&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=88642&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1727,49 +1727,49 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>총리령</t>
+          <t>대통령령</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026.08.13</t>
+          <t>2026.09.16</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026.08.20</t>
+          <t>2026.10.26</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:15:11.945277+09:00</t>
+          <t>2026-09-16 12:15:11.569170+09:00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-08-13 12:15:11.945277+09:00</t>
+          <t>2026-09-16 12:15:11.569170+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>17151</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=87372&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=88084&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1779,39 +1779,39 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>대통령령</t>
+          <t>총리령</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026.06.30</t>
+          <t>2026.08.13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026.08.10</t>
+          <t>2026.08.20</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:16.444527+09:00</t>
+          <t>2026-08-13 12:15:11.945277+09:00</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:16.444527+09:00</t>
+          <t>2026-08-13 12:15:11.945277+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1821,7 +1821,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86980&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=87372&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1836,17 +1836,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026.06.02</t>
+          <t>2026.06.30</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026.07.13</t>
+          <t>2026.08.10</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1863,7 +1863,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1873,7 +1873,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86932&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86980&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026.06.01</t>
+          <t>2026.06.02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1915,17 +1915,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86700&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86932&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>총리령</t>
+          <t>대통령령</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026.05.13</t>
+          <t>2026.06.01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026.05.20</t>
+          <t>2026.07.13</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1967,17 +1967,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85978&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=86700&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1987,22 +1987,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>대통령령</t>
+          <t>총리령</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026.03.16</t>
+          <t>2026.05.13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026.04.27</t>
+          <t>2026.05.20</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2019,17 +2019,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85936&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85978&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2039,22 +2039,22 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>총리령</t>
+          <t>대통령령</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026.03.11</t>
+          <t>2026.03.16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026.03.18</t>
+          <t>2026.04.27</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2071,17 +2071,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>개인정보 보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
+          <t>개인정보보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=84820&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=85936&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025.12.16</t>
+          <t>2026.03.11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2025.12.19</t>
+          <t>2026.03.18</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2025-12-16</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2123,17 +2123,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+          <t>개인정보 보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=83132&amp;lawCd=2000000318612&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=84820&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2143,22 +2143,22 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>대통령령</t>
+          <t>총리령</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025.06.23</t>
+          <t>2025.12.16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2025.08.04</t>
+          <t>2025.12.19</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2025-06-23</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2175,7 +2175,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2185,7 +2185,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=82960&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=83132&amp;lawCd=2000000318612&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2200,17 +2200,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025.05.30</t>
+          <t>2025.06.23</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2025.07.09</t>
+          <t>2025.08.04</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2025-05-30</t>
+          <t>2025-06-23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -2227,50 +2227,102 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>개인정보 보호법 시행령 일부개정령안 입법예고</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=82960&amp;lawCd=0&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>개인정보보호위원회</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>대통령령</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2025.05.30</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2025.07.09</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-05-30</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:16.444527+09:00</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:16.444527+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>개인정보 보호위원회 직제 시행규칙 일부개정령안 입법예고</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/lawinfo/makingInfo.mo?mid=a10104010000&amp;lawSeq=81708&amp;lawCd=2000000315220&amp;lawType=TYPE5&amp;pageCnt=10&amp;currentPage=1&amp;keyField=lmNm&amp;keyWord=&amp;stYdFmt=&amp;edYdFmt=&amp;lsClsCd=&amp;cptOfiOrgCd=%EA%B0%9C%EC%9D%B8%EC%A0%95%EB%B3%B4%EB%B3%B4%ED%98%B8%EC%9C%84%EC%9B%90%ED%9A%8C</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D13" t="inlineStr">
         <is>
           <t>개인정보보호위원회</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>총리령</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>2025.02.07</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>2025.02.14</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2025-02-07</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:16.444527+09:00</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:16.444527+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,17 +465,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>31201</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
+          <t>법제처, 추석 명절을 맞아 공주산성시장 방문</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157132&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,39 +495,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:20.077861+09:00</t>
+          <t>2026-09-16 15:15:18.945495+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:20.077861+09:00</t>
+          <t>2026-09-16 15:15:18.945495+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
+          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,39 +537,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>법제처, 제3회 특별성과 포상 수여</t>
+          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -579,39 +579,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
+          <t>법제처, 제3회 특별성과 포상 수여</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -621,39 +621,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -663,29 +663,29 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -717,27 +717,27 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -747,34 +747,34 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -789,39 +789,39 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -831,39 +831,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -873,39 +873,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -915,29 +915,29 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -969,27 +969,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -999,34 +999,34 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1041,39 +1041,39 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1083,39 +1083,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1125,39 +1125,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1167,39 +1167,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1209,39 +1209,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1251,29 +1251,29 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1305,27 +1305,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1347,27 +1347,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1389,27 +1389,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1431,27 +1431,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1473,27 +1473,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1515,27 +1515,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1557,27 +1557,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1599,40 +1599,82 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2381,7 +2381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2444,27 +2444,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -2479,7 +2479,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2489,34 +2489,34 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -2536,44 +2536,44 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2615,22 +2615,22 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2650,54 +2650,54 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2707,54 +2707,54 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -2774,96 +2774,96 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -2878,106 +2878,106 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -2992,54 +2992,54 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3059,44 +3059,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3116,44 +3116,44 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3173,19 +3173,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3200,7 +3200,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -3230,44 +3230,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3277,7 +3277,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3287,19 +3287,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3344,44 +3344,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3391,49 +3391,49 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -3448,49 +3448,49 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -3527,27 +3527,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -3584,27 +3584,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3619,49 +3619,49 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3676,49 +3676,49 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3733,7 +3733,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -3755,27 +3755,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3812,32 +3812,32 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -3847,7 +3847,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3857,19 +3857,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3884,7 +3884,7 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -3914,44 +3914,44 @@
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -3971,39 +3971,39 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4018,7 +4018,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4040,7 +4040,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4085,39 +4085,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4132,44 +4132,44 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4189,7 +4189,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4211,27 +4211,27 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4251,49 +4251,49 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4303,44 +4303,44 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4360,7 +4360,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -4382,32 +4382,32 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4417,29 +4417,29 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4454,7 +4454,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4484,44 +4484,44 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4531,29 +4531,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4568,7 +4568,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4598,44 +4598,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -4655,19 +4655,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4712,44 +4712,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4769,39 +4769,39 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4838,12 +4838,12 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -4873,7 +4873,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4883,39 +4883,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -4940,39 +4940,39 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -4982,12 +4982,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -4997,44 +4997,44 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -5044,7 +5044,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5054,39 +5054,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5101,49 +5101,49 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -5158,49 +5158,49 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5215,86 +5215,86 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5309,7 +5309,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5329,7 +5329,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -5339,39 +5339,39 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5381,59 +5381,59 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5443,7 +5443,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5453,44 +5453,44 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5500,29 +5500,29 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -5557,7 +5557,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5567,19 +5567,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -5624,44 +5624,44 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5671,54 +5671,54 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5738,39 +5738,39 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -5785,7 +5785,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5795,34 +5795,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -5842,7 +5842,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5864,27 +5864,27 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5921,32 +5921,32 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -5956,44 +5956,44 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6035,22 +6035,22 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -6092,22 +6092,22 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6149,32 +6149,32 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -6194,39 +6194,39 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6251,34 +6251,34 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -6298,49 +6298,49 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6377,32 +6377,32 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -6412,44 +6412,44 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6491,27 +6491,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -6526,54 +6526,54 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6593,44 +6593,44 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -6640,7 +6640,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -6650,44 +6650,44 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6697,7 +6697,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6707,39 +6707,39 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -6749,116 +6749,116 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -6868,49 +6868,49 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -6925,49 +6925,49 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -7004,27 +7004,27 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7039,54 +7039,54 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -7096,54 +7096,54 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -7153,49 +7153,49 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -7210,49 +7210,49 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -7267,7 +7267,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -7289,32 +7289,32 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -7334,39 +7334,39 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7391,39 +7391,39 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7448,44 +7448,44 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7495,7 +7495,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7505,19 +7505,19 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -7527,17 +7527,17 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7552,7 +7552,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7562,44 +7562,44 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7609,7 +7609,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7631,27 +7631,27 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7666,7 +7666,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7688,27 +7688,27 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -7723,7 +7723,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7745,32 +7745,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7780,49 +7780,49 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7837,54 +7837,54 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7894,49 +7894,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -7951,49 +7951,49 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -8008,7 +8008,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -8030,27 +8030,27 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8065,7 +8065,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -8087,32 +8087,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -8122,49 +8122,49 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8179,49 +8179,49 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -8258,32 +8258,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -8293,54 +8293,54 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -8350,7 +8350,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8372,32 +8372,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -8429,32 +8429,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8464,7 +8464,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8486,12 +8486,12 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -8501,17 +8501,17 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8543,27 +8543,27 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -8578,7 +8578,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8600,55 +8600,112 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -10038,7 +10038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K105"/>
+  <dimension ref="A1:K106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10101,7 +10101,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10111,27 +10111,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -10142,19 +10142,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10164,22 +10164,22 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -10190,24 +10190,24 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10217,12 +10217,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10248,44 +10248,44 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -10293,46 +10293,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10342,7 +10338,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -10350,7 +10346,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10358,19 +10358,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10380,22 +10380,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10406,92 +10406,92 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10501,60 +10501,60 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -10562,31 +10562,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -10596,27 +10592,27 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -10631,52 +10627,56 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I12" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10684,34 +10684,34 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -10729,11 +10729,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10741,19 +10737,19 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -10763,12 +10759,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10778,7 +10774,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10798,44 +10794,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10843,27 +10839,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10873,12 +10873,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -10888,35 +10888,35 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10941,103 +10941,103 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11047,35 +11047,35 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11085,22 +11085,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -11116,34 +11116,34 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11161,56 +11161,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -11218,42 +11214,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -11263,7 +11263,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11271,56 +11271,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11328,7 +11324,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11336,19 +11336,19 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11358,27 +11358,27 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
@@ -11389,19 +11389,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11411,12 +11411,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11426,50 +11426,50 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11479,7 +11479,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11487,31 +11487,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -11521,27 +11517,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -11556,34 +11552,34 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -11593,15 +11589,19 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11609,19 +11609,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11631,22 +11631,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -11662,34 +11662,34 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11699,7 +11699,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -11707,11 +11707,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11719,44 +11715,44 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -11764,42 +11760,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -11809,35 +11809,35 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -11847,12 +11847,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11862,12 +11862,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
@@ -11878,44 +11878,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -11923,11 +11923,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11935,52 +11931,56 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11988,19 +11988,19 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12025,7 +12025,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -12041,19 +12041,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12063,50 +12063,50 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12116,22 +12116,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -12147,44 +12147,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -12200,34 +12200,34 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -12248,24 +12248,24 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12290,12 +12290,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
@@ -12306,19 +12306,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12328,50 +12328,50 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12381,12 +12381,12 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -12396,7 +12396,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12407,24 +12407,24 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12460,39 +12460,39 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12510,31 +12510,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12544,12 +12540,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12559,7 +12555,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -12591,7 +12587,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12601,12 +12597,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12616,7 +12612,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -12648,7 +12644,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12658,12 +12654,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12673,7 +12669,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12705,7 +12701,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12715,22 +12711,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -12750,52 +12746,56 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I51" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12803,19 +12803,19 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12825,12 +12825,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -12840,7 +12840,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -12856,19 +12856,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12878,50 +12878,50 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12931,12 +12931,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -12946,7 +12946,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -12962,34 +12962,34 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -13007,64 +13007,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13072,34 +13072,34 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -13109,7 +13109,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -13137,22 +13137,22 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -13170,11 +13170,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13194,22 +13190,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -13219,35 +13215,39 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -13257,12 +13257,12 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -13272,35 +13272,35 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -13325,35 +13325,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13363,22 +13363,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -13394,19 +13394,19 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13416,12 +13416,12 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -13431,7 +13431,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -13447,34 +13447,34 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -13492,56 +13492,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -13549,7 +13545,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I65" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13557,34 +13557,34 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -13605,96 +13605,92 @@
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -13704,7 +13700,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -13712,7 +13708,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I68" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13720,19 +13720,19 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -13742,12 +13742,12 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -13757,12 +13757,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -13773,19 +13773,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13795,22 +13795,22 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -13826,19 +13826,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13848,12 +13848,12 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -13863,7 +13863,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -13874,96 +13874,92 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -13973,35 +13969,39 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14011,22 +14011,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -14037,24 +14037,24 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14064,12 +14064,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -14079,7 +14079,7 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -14090,24 +14090,24 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14117,22 +14117,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -14148,44 +14148,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -14201,44 +14201,44 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -14246,31 +14246,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -14280,12 +14276,12 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -14295,7 +14291,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -14327,22 +14323,22 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -14352,7 +14348,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -14360,27 +14356,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14390,12 +14390,12 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -14405,113 +14405,113 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -14519,31 +14519,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14553,12 +14549,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -14568,7 +14564,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -14600,32 +14596,32 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -14633,7 +14629,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14653,22 +14653,22 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -14678,7 +14678,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -14706,22 +14706,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -14731,19 +14731,15 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14763,7 +14759,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -14773,12 +14769,12 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -14788,7 +14784,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -14820,40 +14816,44 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14873,22 +14873,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -14898,7 +14898,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -14906,11 +14906,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14930,32 +14926,32 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -14963,7 +14959,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr"/>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14971,34 +14971,34 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -15008,7 +15008,7 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -15019,49 +15019,49 @@
       <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -15089,22 +15089,22 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -15114,7 +15114,7 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -15142,32 +15142,32 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -15195,22 +15195,22 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -15220,39 +15220,35 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -15262,27 +15258,27 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -15309,32 +15305,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -15342,52 +15338,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -15415,32 +15415,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -15468,32 +15468,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -15521,32 +15521,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -15554,46 +15554,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -15603,7 +15599,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -15611,52 +15607,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -15684,55 +15684,108 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B105" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C105" t="inlineStr">
+      <c r="C106" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
+      <c r="D106" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E105" t="inlineStr">
+      <c r="E106" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F106" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="G106" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I105" t="inlineStr">
+      <c r="I106" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J105" t="inlineStr">
+      <c r="J106" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr">
+      <c r="K106" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -10038,7 +10038,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K106"/>
+  <dimension ref="A1:K107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10101,7 +10101,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -10111,12 +10111,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10126,7 +10126,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10142,19 +10142,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10164,27 +10164,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -10195,19 +10195,19 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10217,22 +10217,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -10243,24 +10243,24 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10301,44 +10301,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -10346,46 +10346,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -10395,7 +10391,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10403,7 +10399,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10411,19 +10411,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10433,22 +10433,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -10459,92 +10459,92 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -10554,60 +10554,60 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -10615,31 +10615,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10649,27 +10645,27 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -10684,52 +10680,56 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10737,34 +10737,34 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -10774,7 +10774,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -10782,11 +10782,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10794,19 +10790,19 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -10816,12 +10812,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -10831,7 +10827,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10851,44 +10847,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -10896,27 +10892,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -10926,12 +10926,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -10941,35 +10941,35 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -10979,12 +10979,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -10994,103 +10994,103 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11100,35 +11100,35 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11138,22 +11138,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -11169,34 +11169,34 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11214,56 +11214,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -11271,42 +11267,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11316,7 +11316,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11324,56 +11324,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -11381,7 +11377,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11389,19 +11389,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11411,27 +11411,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
@@ -11442,19 +11442,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11464,12 +11464,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -11479,50 +11479,50 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11532,7 +11532,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11540,31 +11540,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11574,27 +11570,27 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -11609,34 +11605,34 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11646,15 +11642,19 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11662,19 +11662,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11684,22 +11684,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -11715,34 +11715,34 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11752,7 +11752,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -11760,11 +11760,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11772,44 +11768,44 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -11817,42 +11813,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -11862,35 +11862,35 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -11900,12 +11900,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -11915,12 +11915,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
@@ -11931,44 +11931,44 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -11976,11 +11976,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11988,52 +11984,56 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12041,19 +12041,19 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -12063,12 +12063,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -12078,7 +12078,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -12094,19 +12094,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12116,50 +12116,50 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -12169,22 +12169,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -12200,44 +12200,44 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -12253,34 +12253,34 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12290,7 +12290,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -12301,24 +12301,24 @@
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12328,12 +12328,12 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -12343,12 +12343,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
@@ -12359,19 +12359,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12381,50 +12381,50 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -12434,12 +12434,12 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12449,7 +12449,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12460,24 +12460,24 @@
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12513,39 +12513,39 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12555,7 +12555,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -12563,31 +12563,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12597,12 +12593,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12612,7 +12608,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -12644,7 +12640,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12654,12 +12650,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12669,7 +12665,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12701,7 +12697,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12711,12 +12707,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12726,7 +12722,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -12758,7 +12754,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12768,22 +12764,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -12803,52 +12799,56 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I52" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12856,19 +12856,19 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12878,12 +12878,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -12893,7 +12893,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -12909,19 +12909,19 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -12931,50 +12931,50 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -12984,12 +12984,12 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -12999,7 +12999,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -13015,34 +13015,34 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -13052,7 +13052,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -13060,64 +13060,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I57" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13125,34 +13125,34 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13162,7 +13162,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -13190,22 +13190,22 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -13215,7 +13215,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -13223,11 +13223,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13247,22 +13243,22 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -13272,35 +13268,39 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -13310,12 +13310,12 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -13325,35 +13325,35 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -13363,12 +13363,12 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -13378,35 +13378,35 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -13416,22 +13416,22 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -13447,19 +13447,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13469,12 +13469,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13484,7 +13484,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -13500,34 +13500,34 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -13537,7 +13537,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -13545,56 +13545,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -13602,7 +13598,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I66" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13610,34 +13610,34 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -13647,7 +13647,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -13658,96 +13658,92 @@
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -13757,7 +13753,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -13765,7 +13761,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13773,19 +13773,19 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -13795,12 +13795,12 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -13810,12 +13810,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
@@ -13826,19 +13826,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13848,22 +13848,22 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -13879,19 +13879,19 @@
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -13901,12 +13901,12 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -13916,7 +13916,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -13927,96 +13927,92 @@
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -14026,35 +14022,39 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14064,22 +14064,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -14090,24 +14090,24 @@
       <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14117,12 +14117,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -14132,7 +14132,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -14143,24 +14143,24 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -14170,22 +14170,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -14201,44 +14201,44 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -14254,44 +14254,44 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -14299,31 +14299,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -14333,12 +14329,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -14348,7 +14344,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -14380,22 +14376,22 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -14405,7 +14401,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -14413,27 +14409,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr"/>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -14443,12 +14443,12 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -14458,113 +14458,113 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -14572,31 +14572,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -14606,12 +14602,12 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -14621,7 +14617,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -14653,32 +14649,32 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -14686,7 +14682,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr"/>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14706,22 +14706,22 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -14731,7 +14731,7 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -14759,22 +14759,22 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -14784,19 +14784,15 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14816,7 +14812,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -14826,12 +14822,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -14841,7 +14837,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -14873,40 +14869,44 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14926,22 +14926,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -14951,7 +14951,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -14959,11 +14959,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14983,32 +14979,32 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -15016,7 +15012,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15024,34 +15024,34 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -15061,7 +15061,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -15072,49 +15072,49 @@
       <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -15142,22 +15142,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -15195,32 +15195,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -15248,22 +15248,22 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -15273,39 +15273,35 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -15315,27 +15311,27 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -15362,32 +15358,32 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -15395,52 +15391,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -15468,32 +15468,32 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -15521,32 +15521,32 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -15574,32 +15574,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -15607,46 +15607,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H103" t="inlineStr"/>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -15656,7 +15652,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -15664,52 +15660,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -15737,55 +15737,108 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B106" t="inlineStr">
+      <c r="B107" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C106" t="inlineStr">
+      <c r="C107" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
+      <c r="D107" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E106" t="inlineStr">
+      <c r="E107" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F107" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="G107" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H106" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
+      <c r="I107" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J106" t="inlineStr">
+      <c r="J107" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr">
+      <c r="K107" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,27 +465,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제처, 추석 명절을 맞아 공주산성시장 방문</t>
+          <t>법제처, 전세사기피해자 주거안정 입법 조치를 위한 ‘찾아가는 법제심사’ 실시</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157132&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157176&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>경제법제국</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,29 +495,29 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:15:18.945495+09:00</t>
+          <t>2026-09-17 16:15:20.031512+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-16 15:15:18.945495+09:00</t>
+          <t>2026-09-17 16:15:20.031512+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>31201</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
+          <t>법제처, 추석 명절을 맞아 공주산성시장 방문</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157132&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,39 +537,39 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:20.077861+09:00</t>
+          <t>2026-09-16 15:15:18.945495+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:20.077861+09:00</t>
+          <t>2026-09-16 15:15:18.945495+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
+          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -579,39 +579,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>법제처, 제3회 특별성과 포상 수여</t>
+          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -621,39 +621,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
+          <t>법제처, 제3회 특별성과 포상 수여</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -663,39 +663,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -705,29 +705,29 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -759,27 +759,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -789,34 +789,34 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -831,39 +831,39 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -873,39 +873,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -915,39 +915,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -957,29 +957,29 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1011,27 +1011,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1041,34 +1041,34 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1083,39 +1083,39 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1125,39 +1125,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1167,39 +1167,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1209,39 +1209,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1293,29 +1293,29 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1347,27 +1347,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1389,27 +1389,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1431,27 +1431,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1473,27 +1473,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1515,27 +1515,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1557,27 +1557,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1599,27 +1599,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1641,40 +1641,82 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -465,27 +465,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>31651</t>
+          <t>31861</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>법제처, 전세사기피해자 주거안정 입법 조치를 위한 ‘찾아가는 법제심사’ 실시</t>
+          <t>법제처, 아시아 법제기구 협의체에 네팔 가입 승인 및 법 접근성 강화 관련 논의</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157176&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157225&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>경제법제국</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -495,39 +495,39 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-17 16:15:20.031512+09:00</t>
+          <t>2026-09-18 11:15:19.901041+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-17 16:15:20.031512+09:00</t>
+          <t>2026-09-18 11:15:19.901041+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>31201</t>
+          <t>31651</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>법제처, 추석 명절을 맞아 공주산성시장 방문</t>
+          <t>법제처, 전세사기피해자 주거안정 입법 조치를 위한 ‘찾아가는 법제심사’ 실시</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157132&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157176&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>경제법제국</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -537,29 +537,29 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:15:18.945495+09:00</t>
+          <t>2026-09-17 16:15:20.031512+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-16 15:15:18.945495+09:00</t>
+          <t>2026-09-17 16:15:20.031512+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>31201</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
+          <t>법제처, 추석 명절을 맞아 공주산성시장 방문</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=157132&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -569,7 +569,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -579,39 +579,39 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:20.077861+09:00</t>
+          <t>2026-09-16 15:15:18.945495+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-09-11 15:00:20.077861+09:00</t>
+          <t>2026-09-16 15:15:18.945495+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27851</t>
+          <t>29141</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
+          <t>법제처, 추석맞이 아동양육시설 봉사활동, 따뜻한 나눔 실천</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -621,39 +621,39 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-09-08 13:30:19.671650+09:00</t>
+          <t>2026-09-11 15:00:20.077861+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>27461</t>
+          <t>27851</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>법제처, 제3회 특별성과 포상 수여</t>
+          <t>불합리한 행정법령 전수조사 첫 성과, 국토교통부 소관 법령 일괄정비안 국무회의 의결</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156753&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -663,39 +663,39 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-09-07 14:00:19.985373+09:00</t>
+          <t>2026-09-08 13:30:19.671650+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25671</t>
+          <t>27461</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
+          <t>법제처, 제3회 특별성과 포상 수여</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156690&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -705,39 +705,39 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-09-03 10:15:21.147736+09:00</t>
+          <t>2026-09-07 14:00:19.985373+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24842</t>
+          <t>25671</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
+          <t>2027년도 법제처 예산안 700억 원 편성, 올해 대비 15.6% 증가</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156497&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -747,29 +747,29 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-09-01 10:00:21.340393+09:00</t>
+          <t>2026-09-03 10:15:21.147736+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>24841</t>
+          <t>24842</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
+          <t>소방공무원 현장 대응 손해배상 보장 강화 및 개인정보 유출 대응 의무 대폭 확대</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156384&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -801,27 +801,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>23411</t>
+          <t>24841</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
+          <t>Strengthening Damage Compensation Guarantee System for Firefighters' On-Site Response</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156385&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>법령정비지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -831,34 +831,34 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-28 15:15:21.414160+09:00</t>
+          <t>2026-09-01 10:00:21.340393+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23411</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
+          <t>법제처, 미래 신기술과 인공지능(AI) 활용 관련 토론의 장 열어</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156162&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>법제자문1담당관</t>
+          <t>법령정비지원과</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -873,39 +873,39 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-28 10:45:20.917220+09:00</t>
+          <t>2026-08-28 15:15:21.414160+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14381</t>
+          <t>23231</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
+          <t>법제처, 공공기관 법제 지원 강화를 위한 수도권ㆍ강원권 현장설명회 개최</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=156157&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>법제자문1담당관</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -915,39 +915,39 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-06 15:00:21.280220+09:00</t>
+          <t>2026-08-28 10:45:20.917220+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14381</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>법제로 완성하는 국가대전환</t>
+          <t>제2회 법령데이터 활용 아이디어 공모전 시상식 개최</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154906&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>기획재정담당관실</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -957,39 +957,39 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-06 08:30:20.431542+09:00</t>
+          <t>2026-08-06 15:00:21.280220+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>12952</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
+          <t>법제로 완성하는 국가대전환</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154855&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>기획재정담당관실</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -999,29 +999,29 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-03 10:00:19.612801+09:00</t>
+          <t>2026-08-06 08:30:20.431542+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>12951</t>
+          <t>12952</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
+          <t>아동학대는 심층 분석, 저작권 침해는 강력 대응... 권익 보호와 산업 경쟁력 동시 강화</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154664&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1053,27 +1053,27 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12951</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
+          <t>In-Depth Analysis of Child Abuse and Stronger Action against Copyright Infringement...</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154665&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>법제교육과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1083,34 +1083,34 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-07-31 11:00:19.812863+09:00</t>
+          <t>2026-08-03 10:00:19.612801+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>11711</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
+          <t>‘이론에서 실무로’ 제34기 법제처 실무수습 성황리에 마쳐</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154410&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법제교육과</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1125,39 +1125,39 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-07-31 09:45:20.988339+09:00</t>
+          <t>2026-07-31 11:00:19.812863+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11711</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>범정부 형벌 합리화 추진단 공식 출범</t>
+          <t>우리 지역 필수 자치법규 마련 현황, 국가법령정보센터에서 한눈에 확인!</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154405&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>파견</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1167,39 +1167,39 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-07-30 10:00:20.929689+09:00</t>
+          <t>2026-07-31 09:45:20.988339+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>4471</t>
+          <t>11311</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
+          <t>범정부 형벌 합리화 추진단 공식 출범</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=154313&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>파견</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1209,39 +1209,39 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-07-13 13:15:20.449920+09:00</t>
+          <t>2026-07-30 10:00:20.929689+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1511</t>
+          <t>4471</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
+          <t>공무원이 직접 만든 ‘AI 법령 비서’ 시범 개시</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152980&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-07-06 10:00:28.103718+09:00</t>
+          <t>2026-07-13 13:15:20.449920+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>1511</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
+          <t>법제처, 역대 처장ㆍ차장 초청 간담회 개최</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152615&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>법제교류협력담당관실</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1293,39 +1293,39 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-07-03 15:15:21.972107+09:00</t>
+          <t>2026-07-06 10:00:28.103718+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>491</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
+          <t>법제처, 한반도 환경위기 공동 대응을 위한 관학연 공동학술대회 개최</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152490&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>법제교류협력담당관실</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1335,29 +1335,29 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:25.972950+09:00</t>
+          <t>2026-07-03 15:15:21.972107+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
+          <t>해수욕장 불꽃놀이는 허용, 일상 범죄와 소비자 피해는 철저히 방어!</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152381&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1389,27 +1389,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
+          <t>Permitting Beach Fireworks, While Strictly Preventing Crime Occurrence and Consumer Harm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152382&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>대변인실</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1431,27 +1431,27 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
+          <t>법제처, ‘호국보훈의 달’ 맞아 광주보훈병원 국가유공자 위문</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152193&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>국가법령정보센터</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1473,27 +1473,27 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
+          <t>법제처, 생성형 AI 기반 대국민 법령검색 서비스 전환 추진</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152053&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>법령정비총괄과</t>
+          <t>국가법령정보센터</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1515,27 +1515,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
+          <t>청년 창업 활성화를 위한 법ㆍ제도 개선, 현장에서 답을 찾다</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=152008&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>자치법제지원과</t>
+          <t>법령정비총괄과</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1557,27 +1557,27 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
+          <t>법제처, 5극3특시대 지방정부의 자율성 확보를 위한 법제 개선의 장 열어</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151899&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>법령정보총괄과</t>
+          <t>자치법제지원과</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1599,27 +1599,27 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
+          <t>법제처, 국내 거주 외국인의 정착 지원 위한 맞춤형 생활법령 서비스 강화</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151696&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>혁신행정감사담당관실</t>
+          <t>법령정보총괄과</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1641,27 +1641,27 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+          <t>법제처, 기관 내 갑질 근절을 위한 ‘안심 상담ㆍ신고 노무사’ 제도 운영</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=151297&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>대변인실</t>
+          <t>혁신행정감사담당관실</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1683,40 +1683,82 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>New Laws will Take Effect to Protect Citizens and Promote Industries</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150887&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>대변인실</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:14:25.972950+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>자율주행 규제 합리화, 해외직구 안전 강화 등 국민보호 · 산업지원 새 법령 시행</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>https://www.moleg.go.kr/board.es?mid=a10501000000&amp;bid=0048&amp;act=view&amp;list_no=150819&amp;tag=&amp;pageCntBySelf=10&amp;nPage=1&amp;keyField=&amp;keyWord=&amp;cg_code=</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>대변인실</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>2026-06-01</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2026-07-02 13:14:25.972950+09:00</t>
         </is>
@@ -10137,7 +10179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:K110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10200,32 +10242,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10233,11 +10275,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10245,19 +10283,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10267,65 +10305,65 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -10335,15 +10373,19 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10351,19 +10393,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -10373,27 +10415,27 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
@@ -10404,19 +10446,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10426,50 +10468,50 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10479,22 +10521,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -10505,49 +10547,49 @@
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -10555,31 +10597,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10589,22 +10627,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -10615,49 +10653,49 @@
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -10665,57 +10703,61 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
@@ -10726,19 +10768,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10748,22 +10790,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -10779,56 +10821,52 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10836,101 +10874,97 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -10938,7 +10972,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10946,19 +10984,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -10968,27 +11006,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11003,34 +11041,34 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -11040,7 +11078,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -11048,11 +11086,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11060,44 +11094,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -11105,60 +11139,68 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11166,19 +11208,19 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -11188,12 +11230,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -11203,7 +11245,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -11219,44 +11261,44 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -11272,19 +11314,19 @@
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11294,22 +11336,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -11325,97 +11367,97 @@
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -11423,31 +11465,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11457,22 +11495,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -11488,19 +11526,19 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11510,22 +11548,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -11545,19 +11583,19 @@
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11567,22 +11605,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11593,57 +11631,61 @@
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11651,19 +11693,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -11673,22 +11715,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -11699,39 +11741,39 @@
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -11741,19 +11783,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11761,101 +11799,97 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -11863,7 +11897,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I32" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11871,52 +11909,56 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I33" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11924,44 +11966,44 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -11969,11 +12011,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11981,44 +12019,44 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -12029,57 +12067,61 @@
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12087,34 +12129,34 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -12124,7 +12166,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -12135,61 +12177,57 @@
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12197,19 +12235,19 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12219,27 +12257,27 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -12250,52 +12288,56 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12303,19 +12345,19 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -12325,50 +12367,50 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12378,75 +12420,75 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -12462,19 +12504,19 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12484,22 +12526,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12510,39 +12552,39 @@
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -12552,35 +12594,35 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -12590,22 +12632,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12616,24 +12658,24 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12643,27 +12685,27 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -12674,19 +12716,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12696,12 +12738,12 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -12711,7 +12753,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -12727,34 +12769,34 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12764,7 +12806,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12772,11 +12814,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12784,34 +12822,34 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12821,7 +12859,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -12829,31 +12867,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -12863,12 +12897,12 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -12878,7 +12912,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -12910,7 +12944,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -12920,12 +12954,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -12967,7 +13001,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -12977,22 +13011,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -13012,52 +13046,56 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13065,52 +13103,56 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I55" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13118,19 +13160,19 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -13140,50 +13182,50 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13193,65 +13235,65 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -13261,7 +13303,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -13269,117 +13311,117 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I60" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13387,34 +13429,34 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -13424,7 +13466,7 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -13432,11 +13474,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13456,22 +13494,22 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -13481,50 +13519,50 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -13534,7 +13572,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -13542,7 +13580,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13550,19 +13592,19 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -13572,12 +13614,12 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13587,7 +13629,7 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
@@ -13603,19 +13645,19 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13625,50 +13667,50 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13678,22 +13720,22 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -13709,34 +13751,34 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -13746,7 +13788,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -13754,56 +13796,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -13814,49 +13852,49 @@
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -13864,64 +13902,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13929,19 +13967,19 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -13951,65 +13989,65 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -14019,15 +14057,19 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I72" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14035,19 +14077,19 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -14057,27 +14099,27 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
@@ -14088,19 +14130,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14110,22 +14152,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -14136,61 +14178,57 @@
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14198,19 +14236,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14220,22 +14258,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -14251,52 +14289,56 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14304,19 +14346,19 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -14326,22 +14368,22 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -14357,19 +14399,19 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -14379,22 +14421,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -14405,49 +14447,49 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -14463,44 +14505,44 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -14508,56 +14550,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H81" t="inlineStr"/>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -14565,46 +14603,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -14614,7 +14648,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -14622,42 +14656,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -14667,15 +14705,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14683,44 +14725,44 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -14736,56 +14778,52 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14793,44 +14831,44 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -14838,56 +14876,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -14895,7 +14929,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr"/>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14915,32 +14953,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -14948,7 +14986,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr"/>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14968,22 +15010,22 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -14993,19 +15035,15 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15025,22 +15063,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -15050,19 +15088,15 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
       <c r="I91" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15082,40 +15116,44 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15135,7 +15173,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -15145,27 +15183,27 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15192,7 +15230,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -15202,22 +15240,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -15233,44 +15271,44 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -15278,52 +15316,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -15334,49 +15376,49 @@
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -15404,32 +15446,32 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -15457,89 +15499,85 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H99" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -15547,109 +15585,109 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -15657,52 +15695,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -15730,32 +15772,32 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -15783,32 +15825,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -15816,56 +15858,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -15893,32 +15931,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -15926,75 +15964,185 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>51749</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B108" t="inlineStr">
+      <c r="B110" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C108" t="inlineStr">
+      <c r="C110" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D110" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E110" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F110" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G110" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I110" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J110" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K110" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2465,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,32 +2528,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2563,54 +2563,54 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2620,49 +2620,49 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -2687,34 +2687,34 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2734,44 +2734,44 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2813,22 +2813,22 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2848,54 +2848,54 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2905,54 +2905,54 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2972,96 +2972,96 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -3076,106 +3076,106 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-11 11:15:28.934341+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>57531</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>384</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -3190,54 +3190,54 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>23</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-10 15:46:08.706294+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57141</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1302</t>
+          <t>1303</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
+          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3247,7 +3247,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -3257,44 +3257,44 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-04 10:00:24.513793+09:00</t>
+          <t>2026-09-10 11:00:27.246391+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>50941</t>
+          <t>52141</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1301</t>
+          <t>1302</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
+          <t>개인정보위, 2027년 예산안 996억 원 반영❶예방‧보호, ❷AX 혁신 안전 활용에 중점 투자</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12442</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -3314,44 +3314,44 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-02 15:30:28.387895+09:00</t>
+          <t>2026-09-04 10:00:24.513793+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>49901</t>
+          <t>50941</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1301</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
+          <t>‘보이스피싱 근절 종합대책’ 1년, 발생건수 40%·피해액 43% 감소 성과</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12440</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2020</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -3371,19 +3371,19 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-02 15:30:28.387895+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>48941</t>
+          <t>49901</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2020</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -3428,44 +3428,44 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-08-31 11:00:26.848516+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>49902</t>
+          <t>48941</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1299</t>
+          <t>1300</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
+          <t>개인정보위, ㈜지에스리테일 유출사고에 대해 과징금 128억 3,600만 원, 과태료 300만 원 부과</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12425</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -3475,7 +3475,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1917</t>
+          <t>10</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -3485,19 +3485,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-31 11:00:26.848516+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>46561</t>
+          <t>49902</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1917</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -3542,44 +3542,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-08-28 12:00:26.392609+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>46561</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1299</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>인공지능 시대 개인정보 보호와 활용, 최고의 미래 법률 전문가는?</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12421</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -3589,49 +3589,49 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1955</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-28 12:00:26.392609+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49905</t>
+          <t>49911</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -3646,49 +3646,49 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2508</t>
+          <t>1955</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49904</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2889</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -3725,27 +3725,27 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49903</t>
+          <t>49904</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -3760,7 +3760,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2796</t>
+          <t>2889</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -3782,27 +3782,27 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>46031</t>
+          <t>49903</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>383</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -3817,49 +3817,49 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2796</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-27 15:31:06.679425+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>45663</t>
+          <t>46031</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1296</t>
+          <t>383</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
+          <t>개인정보보호위원회 개인정보관리 전문기관 지정 공고(공고 제2026-109호)</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12416</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -3874,49 +3874,49 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-27 11:00:26.295039+09:00</t>
+          <t>2026-08-27 15:31:06.679425+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>45663</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1297</t>
+          <t>1296</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
+          <t>실종아동과 입양인 개인정보 유출한 국가아동권리보장원 제재</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12413</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -3953,27 +3953,27 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45661</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1298</t>
+          <t>1297</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
+          <t>개인정보위, 안전조치 의무를 위반한 HD현대그룹 소속 2개 사업자 제재</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12414</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4010,32 +4010,32 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>49906</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1298</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
+          <t>개인정보위, 금융분야 불필요한 주민등록번호 처리 관행 개선</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12415</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4045,7 +4045,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>3052</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -4055,19 +4055,19 @@
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-27 11:00:26.295039+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>44101</t>
+          <t>49906</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3052</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -4112,44 +4112,44 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-25 12:00:28.630385+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>49908</t>
+          <t>44101</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1293</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>정부, 공공부문 개인정보 보호 역량 강화 위한 인력 확충한다</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12411</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2780</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -4169,39 +4169,39 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-08-25 12:00:28.630385+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>49908</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>3055</t>
+          <t>2780</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -4238,7 +4238,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43521</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3055</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -4283,39 +4283,39 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 15:00:28.011868+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>43452</t>
+          <t>43521</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 2026년 공공기관 개인정보 보호수준 평가단 위촉</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12402</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -4330,44 +4330,44 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-24 14:01:07.394147+09:00</t>
+          <t>2026-08-24 15:00:28.011868+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>43451</t>
+          <t>43452</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -4409,27 +4409,27 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>43121</t>
+          <t>43451</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1294</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4449,49 +4449,49 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-24 10:00:26.766249+09:00</t>
+          <t>2026-08-24 14:01:07.394147+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>49913</t>
+          <t>43121</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>381</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
+          <t>개인정보위, 제3회 ‘개인정보 고래상’ 시상</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12400</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4501,44 +4501,44 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2691</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-24 10:00:26.766249+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>49912</t>
+          <t>49913</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>382</t>
+          <t>381</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
+          <t>「과징금 투자 감경제도 안내서」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12398</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>2691</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -4580,32 +4580,32 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>49909</t>
+          <t>49912</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>382</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
+          <t>「개인정보 유출등 대응 매뉴얼」 초안 공개 및 의견수렴</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12399</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4615,29 +4615,29 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>40381</t>
+          <t>49909</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>8518</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -4682,44 +4682,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-20 16:45:27.227566+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>49914</t>
+          <t>40381</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>380</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
+          <t>안전한 인공지능 개발을 위한 개인정보 활용 특례 신설 「개인정보 보호법」 개정안 국회 본회의 통과</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12391</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4729,29 +4729,29 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>8808</t>
+          <t>39</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-20 16:45:27.227566+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>39131</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -4786,7 +4786,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>8808</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -4796,44 +4796,44 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-19 11:16:06.252027+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>49915</t>
+          <t>39131</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>380</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>(대법원) 스크래핑 차단 한시적 유예 신청(~8.31.) 안내</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12387</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4843,7 +4843,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4957</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -4853,19 +4853,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-19 11:16:06.252027+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>35591</t>
+          <t>49915</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -4910,44 +4910,44 @@
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-14 18:16:08.177242+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>35591</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12379</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4957,7 +4957,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>5234</t>
+          <t>12</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -4967,39 +4967,39 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-14 18:16:08.177242+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>49916</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -5014,7 +5014,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>5492</t>
+          <t>5234</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -5036,12 +5036,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>34711</t>
+          <t>49916</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>379</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -5081,39 +5081,39 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-13 17:31:09.311303+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>34691</t>
+          <t>34711</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>378</t>
+          <t>379</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
+          <t>「국경 간 개인정보 보호 규칙 인증제도의 운영에 관한 지침」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12376</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -5123,12 +5123,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -5138,39 +5138,39 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-13 17:16:11.373869+09:00</t>
+          <t>2026-08-13 17:31:09.311303+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34691</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>378</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
+          <t>2026년 개인정보보호 유공 정부포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12375</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -5195,44 +5195,44 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:08.209725+09:00</t>
+          <t>2026-08-13 17:16:11.373869+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>49918</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>377</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>「개인정보 보호위원회 직제 시행규칙」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12370</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -5242,7 +5242,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>9323</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -5252,39 +5252,39 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-13 09:31:08.209725+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>49910</t>
+          <t>49918</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -5299,49 +5299,49 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>8923</t>
+          <t>9323</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-09-01 12:45:28.346474+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>32571</t>
+          <t>49910</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>376</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -5356,49 +5356,49 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>8923</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-11 11:16:08.723253+09:00</t>
+          <t>2026-09-01 12:45:28.346474+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>32541</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>376</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(8.11.~31.) 안내</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12368</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -5413,86 +5413,86 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>2026-08-11 11:00:26.976860+09:00</t>
+          <t>2026-08-11 11:16:08.723253+09:00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>49919</t>
+          <t>32541</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
+          <t>개인정보위, 본인전송요구 대리인의 사전협의 시범운영(3차) 추가신청 받는다</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12367</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-08-11 11:00:26.976860+09:00</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>28831</t>
+          <t>49919</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -5537,39 +5537,39 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>2026-08-06 15:46:06.392884+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>28361</t>
+          <t>28831</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>1290</t>
+          <t>375</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
+          <t>2026년 민원서비스 종합평가 고충민원 만족도·신뢰도 측정을 위한 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12362</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -5579,59 +5579,59 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-08-06 10:00:26.758706+09:00</t>
+          <t>2026-08-06 15:46:06.392884+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22661</t>
+          <t>28361</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1289</t>
+          <t>1290</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
+          <t>인공지능(AI) 시대 개인정보 제도 혁신, 국민과 함께 설계한다</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12361</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -5651,44 +5651,44 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-30 10:30:27.268351+09:00</t>
+          <t>2026-08-06 10:00:26.758706+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>49920</t>
+          <t>22661</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>374</t>
+          <t>1289</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>개인정보 영향평가기관 지정갱신 공고</t>
+          <t>개인정보위, ‘㈜KT의개인정보 유출사고’ 제재처분 의결</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12349</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -5698,29 +5698,29 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>9909</t>
+          <t>50</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-09-01 12:46:08.751558+09:00</t>
+          <t>2026-07-30 10:30:27.268351+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>22391</t>
+          <t>49920</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -5755,7 +5755,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -5765,19 +5765,19 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-29 17:16:05.593491+09:00</t>
+          <t>2026-09-01 12:46:08.751558+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>22351</t>
+          <t>22391</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -5792,7 +5792,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12346</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -5812,7 +5812,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -5822,44 +5822,44 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-29 16:46:07.286593+09:00</t>
+          <t>2026-07-29 17:16:05.593491+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>17701</t>
+          <t>22351</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>374</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
+          <t>개인정보 영향평가기관 지정갱신 공고</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12345</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -5869,54 +5869,54 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-24 10:00:27.219427+09:00</t>
+          <t>2026-07-29 16:46:07.286593+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>17362</t>
+          <t>17701</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
+          <t>유럽연합, 한국 개인정보 보호 수준 재확인… 적정성 결정 유지</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12333</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -5936,39 +5936,39 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-23 16:00:30.422263+09:00</t>
+          <t>2026-07-24 10:00:27.219427+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>17362</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1285</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
+          <t>「2026 개인정보 미래포럼」 제3차 전체회의 개최</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12329</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5993,34 +5993,34 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>2026-07-23 10:00:38.625145+09:00</t>
+          <t>2026-07-23 16:00:30.422263+09:00</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16882</t>
+          <t>16883</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>1286</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
+          <t>국민이 신뢰할 수 있는 공공 인공지능 전환(AX),프라이버시 보호로 적극 뒷받침</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12307</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -6040,7 +6040,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -6062,27 +6062,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16881</t>
+          <t>16882</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1287</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
+          <t>대도약의 골든타임, 초격차 성장동력 확보와 AI 생태계 발전기반 강화</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12308</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -6119,32 +6119,32 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16314</t>
+          <t>16881</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>370</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
+          <t>개인정보위, 적법 근거 없이 개인정보수집·이용한 틱톡·애플 제재</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12330</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -6154,44 +6154,44 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-22 13:01:11.478354+09:00</t>
+          <t>2026-07-23 10:00:38.625145+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16313</t>
+          <t>16314</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>371</t>
+          <t>370</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호위원회의 조사 및 처분에 관한 규정」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12309</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -6211,7 +6211,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -6233,22 +6233,22 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>16313</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>372</t>
+          <t>371</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 고발 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12310</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -6290,22 +6290,22 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>16311</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>372</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
+          <t>「개인정보 보호 법규 위반에 대한 징계권고 기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12311</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -6325,7 +6325,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -6347,32 +6347,32 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14451</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>369</t>
+          <t>373</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
+          <t>「개인정보 보호법 위반에 대한 공표 및 공표명령 지침」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12312</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -6382,7 +6382,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -6392,39 +6392,39 @@
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 10:16:06.541093+09:00</t>
+          <t>2026-07-22 13:01:11.478354+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14433</t>
+          <t>14451</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>366</t>
+          <t>369</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간 추가운영(7.20.~31.) 안내</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12289</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>14</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -6449,34 +6449,34 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:08.116520+09:00</t>
+          <t>2026-07-20 10:16:06.541093+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>14422</t>
+          <t>14433</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>366</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12278</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -6496,49 +6496,49 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-20 10:00:27.102836+09:00</t>
+          <t>2026-07-20 10:01:08.116520+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14422</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
+          <t>「개인정보 이노베이션 존」 신규 운영기관 공모</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12287</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -6575,32 +6575,32 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11392</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
+          <t>개인정보위, ‘본인전송요구권’ 사전협의 지원 시범운영 7월 31일까지 추가신청 받는다</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12288</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -6610,44 +6610,44 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-16 13:01:06.075969+09:00</t>
+          <t>2026-07-20 10:00:27.102836+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11391</t>
+          <t>11392</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>368</t>
+          <t>367</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
+          <t>「개인정보 보호법 위반에 대한 과징금 부과기준」 일부개정안 행정예고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12282</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -6667,7 +6667,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -6689,27 +6689,27 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11221</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>368</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
+          <t>「개인정보 보호법 위반에 대한 과태료 부과기준」 제정안 행정예고</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12284</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -6724,54 +6724,54 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-16 11:00:27.819143+09:00</t>
+          <t>2026-07-16 13:01:06.075969+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>11221</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
+          <t>AI 혁신을 뒷받침하고 국민 권익을 증진하는 예방중심 개인정보 보호 실현</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12281</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>33</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -6791,44 +6791,44 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-15 09:45:30.272302+09:00</t>
+          <t>2026-07-16 11:00:27.819143+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9501</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.15.자)</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12276</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>인프라표준화팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -6838,7 +6838,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>25</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6848,44 +6848,44 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-14 10:00:29.933870+09:00</t>
+          <t>2026-07-15 09:45:30.272302+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>9381</t>
+          <t>9501</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>1279</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
+          <t>개인정보 전송요구권 전송체계 기술적 기틀, 고용⋅교육 부문까지 확대 마련</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12266</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>범정부마이데이터추진단 전략기획팀</t>
+          <t>인프라표준화팀</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6895,7 +6895,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -6905,39 +6905,39 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-14 08:30:26.475160+09:00</t>
+          <t>2026-07-14 10:00:29.933870+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>9271</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>365</t>
+          <t>1280</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
+          <t>정보주체의 본인전송요구권, 더 안전하게 이용할 수 있습니다</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12273</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>법무감사담당관</t>
+          <t>범정부마이데이터추진단 전략기획팀</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -6947,116 +6947,116 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>303</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-13 17:16:17.898453+09:00</t>
+          <t>2026-07-14 08:30:26.475160+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6541</t>
+          <t>9271</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>1278</t>
+          <t>365</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
+          <t>공공기관 종합청렴도 평가 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12267</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>조사2과</t>
+          <t>법무감사담당관</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>13</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:00:31.832545+09:00</t>
+          <t>2026-07-13 17:16:17.898453+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5491</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>1278</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
+          <t>개인정보 온라인 불법유통 청년들이 직접 차단한다.</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12262</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>조사2과</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -7066,49 +7066,49 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 11:01:05.002078+09:00</t>
+          <t>2026-07-10 14:00:31.832545+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5491</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1276</t>
+          <t>364</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
+          <t>제4회 개인정보보호 모의재판 경연대회 참가자 모집</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12245</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>장석인</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -7123,49 +7123,49 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>22</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 10:00:57.524524+09:00</t>
+          <t>2026-07-09 11:01:05.002078+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5402</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1276</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
+          <t>개인정보위, 안전조치 의무 위반 3개 사업자 제재</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12242</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>침해평가과</t>
+          <t>장석인</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -7202,27 +7202,27 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>363</t>
+          <t>1277</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
+          <t>미래의 개인정보 법률 전문가 모여 인공지능 시대 법적 쟁점 논의한다</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12243</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>침해평가과</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -7237,54 +7237,54 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>2026-07-09 09:46:03.809898+09:00</t>
+          <t>2026-07-09 10:00:57.524524+09:00</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4581</t>
+          <t>5391</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>1275</t>
+          <t>363</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
+          <t>「개인정보 보호책임자 경력 인정에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12244</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -7294,54 +7294,54 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-08 10:00:27.128578+09:00</t>
+          <t>2026-07-09 09:46:03.809898+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>4581</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
+          <t>개인정보위, 응용프로그램 인터페이스(API) 활용 확대에 따른 개인정보 유출 예방 당부</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12241</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -7351,49 +7351,49 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-06 13:46:04.662402+09:00</t>
+          <t>2026-07-08 10:00:27.128578+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>362</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
+          <t>2026년 가명정보 활용 지원체계 설명회 개최 안내</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12238</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -7408,49 +7408,49 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>18</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-06 12:45:29.985993+09:00</t>
+          <t>2026-07-06 13:46:04.662402+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>3181</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>1274</t>
+          <t>1273</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
+          <t>개인정보 처리방침 평가, 국민 눈높이에서 더 꼼꼼히 본다</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12236</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -7465,7 +7465,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>60</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -7487,32 +7487,32 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>3181</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>1274</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
+          <t>개인정보위, 교육‧고용 분야까지 개인정보 제3자 전송요구권 확대 추진</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12237</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7522,7 +7522,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>58</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7532,39 +7532,39 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>2026-07-03 16:00:28.543767+09:00</t>
+          <t>2026-07-06 12:45:29.985993+09:00</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>1043</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1272</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
+          <t>개인정보위, 대전에서 ‘찾아가는 개인정보 현장 컨설팅 및 교육’ 개최</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12227</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7589,39 +7589,39 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>2026-07-03 15:30:33.546332+09:00</t>
+          <t>2026-07-03 16:00:28.543767+09:00</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1271</t>
+          <t>1272</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.3.자)</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12229</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -7636,7 +7636,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -7646,44 +7646,44 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>2026-07-03 10:00:33.422568+09:00</t>
+          <t>2026-07-03 15:30:33.546332+09:00</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>561</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1271</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
+          <t>신뢰로 여는 인공지능(AI) 혁신, 달라지는 개인정보 체계로 이끈다</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12228</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>데이터안전정책과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-03</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7693,7 +7693,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -7703,19 +7703,19 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>2026-07-02 16:45:30.717611+09:00</t>
+          <t>2026-07-03 10:00:33.422568+09:00</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>281</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -7725,17 +7725,17 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
+          <t>개인정보위, 인공지능(AI) 시대 데이터 혁신적 활용을 지역 주도로 확산한다.</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12225</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -7750,7 +7750,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>8</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -7760,44 +7760,44 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 16:45:30.717611+09:00</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1269</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
+          <t>개인정보위, 개인정보보호 현장 간담회 개최</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12224</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>조사1과</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>98</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -7829,27 +7829,27 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>1267</t>
+          <t>1266</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
+          <t>글로벌 개인정보 감독기구에 인공지능(AI) 대응 ‘실전해법’ 제시</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12218</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>1074</t>
+          <t>924</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -7886,27 +7886,27 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1268</t>
+          <t>1267</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
+          <t>투숙객 개인정보보호에 앞장선 호텔, 호텔업 등급평가시 우대</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12219</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -7921,7 +7921,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>1074</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -7943,32 +7943,32 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>361</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.7.1.자)</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12220</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>범정부 마이데이터추진단</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -7978,49 +7978,49 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1842</t>
+          <t>743</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>361</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12216</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>범정부 마이데이터추진단</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -8035,54 +8035,54 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>1029</t>
+          <t>1842</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>360</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
+          <t>(인사발령) 개인정보보호위원회 인사발령('26.6.30.자)</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12217</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8092,49 +8092,49 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>1029</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>1262</t>
+          <t>360</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12202</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -8149,49 +8149,49 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>1263</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
+          <t>개인정보위원장, G7 개인정보 감독기구 라운드테이블 참석</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12201</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>2092</t>
+          <t>2144</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -8228,27 +8228,27 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>1264</t>
+          <t>1263</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>AI 범죄 대응 범부처 협의체 출범</t>
+          <t>「2026 개인정보 보호·활용 기술 대상」 참여기업 모집</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12203</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>인공지능프라이버시팀</t>
+          <t>신기술개인정보과</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>2638</t>
+          <t>2092</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -8285,32 +8285,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>359</t>
+          <t>1264</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
+          <t>AI 범죄 대응 범부처 협의체 출범</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12204</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>인공지능프라이버시팀</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8320,49 +8320,49 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>3745</t>
+          <t>2638</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>1260</t>
+          <t>359</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
+          <t>본인전송요구 대리인의 사전협의 요청 시범기간(6.25.~7.10.) 운영 안내</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12200</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -8377,49 +8377,49 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>2754</t>
+          <t>3745</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>2026-07-02 13:14:32.838364+09:00</t>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1261</t>
+          <t>1260</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
+          <t>개인정보위, 상조서비스 개인정보 보호 취약요인 선제 점검</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12197</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>전략기획팀</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>3085</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -8456,32 +8456,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
+          <t>개인정보위, 국민이 필요로 하는 정보 중심 ‘본인전송요구권’ 안착 지원한다</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12198</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>전략기획팀</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8491,54 +8491,54 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>7681</t>
+          <t>3085</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:09.583121+09:00</t>
+          <t>2026-07-02 13:14:32.838364+09:00</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>357</t>
+          <t>358</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
+          <t>정보보호 및 개인정보보호 관리체계 심사기관 지정 공고(제2026-73호)</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12185</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-06-12</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>6533</t>
+          <t>7681</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -8570,32 +8570,32 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>356</t>
+          <t>357</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
+          <t>「자율기구 공공실태점검단 설치 및 운영에 관한 규정」 발령(2026-70)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12174</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-12</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -8627,32 +8627,32 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>352</t>
+          <t>356</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
+          <t>공공기관 개인정보 보호수준 평가단원 지원 공고</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12160</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>11169</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -8684,12 +8684,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>352</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -8699,17 +8699,17 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12126</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>조사총괄과</t>
+          <t>개인정보보호정책과</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>13472</t>
+          <t>11169</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -8741,27 +8741,27 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>355</t>
+          <t>354</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>「개인정보 보호법 시행령」 일부개정령안 입법예고</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12131</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>신기술개인정보과</t>
+          <t>조사총괄과</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -8776,7 +8776,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>9724</t>
+          <t>13472</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -8798,55 +8798,112 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12136</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>신기술개인정보과</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>9724</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:09.583121+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
+      <c r="B113" t="inlineStr">
         <is>
           <t>353</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>「개인정보 처리 방법에 관한 고시」 일부개정고시안 행정예고</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
+      <c r="D113" t="inlineStr">
         <is>
           <t>https://www.pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12127</t>
         </is>
       </c>
-      <c r="E112" t="inlineStr">
+      <c r="E113" t="inlineStr">
         <is>
           <t>전략기획팀</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F113" t="inlineStr">
         <is>
           <t>2026-05-28</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
         <is>
           <t>11519</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr">
+      <c r="I113" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J112" t="inlineStr">
+      <c r="J113" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr">
+      <c r="K113" t="inlineStr">
         <is>
           <t>2026-07-02 13:15:09.583121+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -8920,7 +8920,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8968,12 +8968,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026년 개인정보 보호주간(9.28.~10.2.) 포스터 및 앰블럼</t>
+          <t>제6회 개인정보 보호의 날(9.30.) 기념식 개최</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8983,39 +8983,39 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20917</t>
+          <t>20920</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20917</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20920</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:39.797854+09:00</t>
+          <t>2026-09-19 14:16:49.840552+09:00</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-08 11:31:39.797854+09:00</t>
+          <t>2026-09-19 14:16:49.840552+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 인증시험(2차) 안내</t>
+          <t>2026년 개인정보 보호주간(9.28.~10.2.) 포스터 및 앰블럼</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -9025,39 +9025,39 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>20917</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20915</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20917</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:16:40.776731+09:00</t>
+          <t>2026-09-08 11:31:39.797854+09:00</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-03 14:16:40.776731+09:00</t>
+          <t>2026-09-08 11:31:39.797854+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
+          <t>2026년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -9067,39 +9067,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20909</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20915</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-10 18:01:43.365104+09:00</t>
+          <t>2026-09-03 14:16:40.776731+09:00</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-10 18:01:43.365104+09:00</t>
+          <t>2026-09-03 14:16:40.776731+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
+          <t>개인정보 포털 예방점검에 따른 서비스 중단 안내 (8.13 19:00 ~ 23:00)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -9109,39 +9109,39 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20908</t>
+          <t>20909</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20909</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-07-09 10:02:18.348370+09:00</t>
+          <t>2026-08-10 18:01:43.365104+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
+          <t>SKT  휴대폰 본인확인서비스 중단 공지(7.12 01:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -9151,39 +9151,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20907</t>
+          <t>20908</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20908</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-07-02 13:16:19.799934+09:00</t>
+          <t>2026-07-09 10:02:18.348370+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
+          <t>2026년 개인정보 영향평가 전문교육(하반기) 안내</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -9193,17 +9193,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20906</t>
+          <t>20907</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20907</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -9220,12 +9220,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
+          <t>정보주체 권리행사(본인확인 내역조회, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.6.16 (화) 19:00 ~20:00)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -9235,17 +9235,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20903</t>
+          <t>20906</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20906</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -9262,12 +9262,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
+          <t>개인정보보호 중심 설계(PbD) 시범인증 참여제품 모집 공고</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-26</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20900</t>
+          <t>20903</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20903</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -9304,12 +9304,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
+          <t>개인정보 포털 DB점검에 따른 서비스 중단 안내 (5.26 19:00 ~ 21:00)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -9319,17 +9319,17 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20896</t>
+          <t>20900</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20900</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -9346,12 +9346,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>제3기 가명정보 전문가 풀 모집 공고</t>
+          <t>(복구완료) 외국인 실명확인 서비스 장애 안내(26.05.19 13:47 ~18:50 )</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -9361,17 +9361,17 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20895</t>
+          <t>20896</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20896</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -9388,12 +9388,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
+          <t>제3기 가명정보 전문가 풀 모집 공고</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -9403,17 +9403,17 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-05-07</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20894</t>
+          <t>20895</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20895</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -9430,12 +9430,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
+          <t>SKT 휴대폰 본인확인서비스 중단 공지(5.10 03:20 ~ 03:25 / 5.12 03:20 ~ 03:25)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -9445,17 +9445,17 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20893</t>
+          <t>20894</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20894</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -9472,12 +9472,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
+          <t>2026년 개인정보 영향평가 인증시험(1차) 안내</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -9487,17 +9487,17 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20893</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20893</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -9514,12 +9514,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
+          <t>본인인증 서비스 장애 발생 공지(2026.04.28(화)15:00 ~ 15:10)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -9529,17 +9529,17 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20884</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20888</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -9556,12 +9556,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
+          <t>개인정보 영향평가 전문인력 인증서 발급 및 유효기간 관련 안내</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -9571,17 +9571,17 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20878</t>
+          <t>20884</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20884</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -9598,12 +9598,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
+          <t>2026년 개인정보 영향평가 계속교육 일정 안내</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -9613,17 +9613,17 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20875</t>
+          <t>20878</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20878</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -9640,12 +9640,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.4.8 (수) 03:00 ~05:00)</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -9655,17 +9655,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20874</t>
+          <t>20875</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20875</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -9682,12 +9682,12 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
+          <t>본인확인 서비스 작업 공지 안내 (2026년 3월 24일(화) 23:00~ 3월 25일(수) 02:00)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20873</t>
+          <t>20874</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20874</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -9724,12 +9724,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24(화)22:00 ~ 2026.03.25(수) 02:00)</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -9744,12 +9744,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20872</t>
+          <t>20873</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20873</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -9766,12 +9766,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>외국인 실명확인 서비스 작업 공지 안내</t>
+          <t>2026년 개인정보 영향평가 전문교육(상반기) 안내</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -9781,17 +9781,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20871</t>
+          <t>20872</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20872</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9808,12 +9808,12 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
+          <t>외국인 실명확인 서비스 작업 공지 안내</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -9823,17 +9823,17 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20870</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20871</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9850,12 +9850,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.03.24. (화) 02:00 ~ 04:00)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -9865,17 +9865,17 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-01-22</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20868</t>
+          <t>20870</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20870</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9892,12 +9892,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.22 (목) 22:00 ~2026.01.23 (금) 05:00)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -9907,17 +9907,17 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-01-20</t>
+          <t>2026-01-22</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20867</t>
+          <t>20868</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20868</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -9934,12 +9934,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
+          <t>본인확인 서비스 작업 공지 안내(2026.01.21 (수) 19:00 ~21:00)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -9949,17 +9949,17 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20866</t>
+          <t>20867</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20867</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -9976,12 +9976,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
+          <t>개인정보 포털 사용자 편의성 설문조사 참여 이벤트 당첨자 발표</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -9991,17 +9991,17 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-01-08</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20865</t>
+          <t>20866</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20866</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -10018,12 +10018,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
+          <t>2026년도 개인정보 보호·활용 분야 R&amp;amp;D 사업 신규지원 대상과제 공고(~2.10. 오후 3시)</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -10033,17 +10033,17 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-08</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20862</t>
+          <t>20865</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20865</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -10060,12 +10060,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
+          <t>정보주체 권리행사(본인인증 내역확인, 웹사이트 회원탈퇴) 서비스 일시 중단 안내 (2026.1.12 (월) 05:00 ~06:00)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -10075,17 +10075,17 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20856</t>
+          <t>20862</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20862</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -10102,12 +10102,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
+          <t>「개인정보관리 전문기관 지정 심사위원회」 심사위원 모집 안내 (~12.23. 18시까지)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -10117,17 +10117,17 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20855</t>
+          <t>20856</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20856</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -10144,12 +10144,12 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+          <t>외국인 본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.17 (수) 16:00 ~17:00)</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -10164,12 +10164,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20854</t>
+          <t>20855</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20855</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -10186,40 +10186,82 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>본인확인/아이핀/실명확인 서비스 일시 중단 안내(2025.12.15 (월) 08:00 ~09:00)</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>관리자</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>20854</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20854</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:16:19.799934+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>2025년 개인정보 영향평가 인증시험(2차) 안내</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>관리자</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
+      <c r="D32" t="inlineStr">
         <is>
           <t>2025-08-25</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>20837</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>https://www.privacy.go.kr/front/bbs/bbsView.do?bbsNo=BBSMSTR_000000000001&amp;bbscttNo=20837</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>2026-07-02 13:16:19.799934+09:00</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2026-07-02 13:16:19.799934+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -10278,7 +10278,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10341,22 +10341,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>63068</t>
+          <t>64631</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>990</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>대국민 혁신 정책·제안 공모전 개최</t>
+          <t>한국인터넷진흥원, 인터넷 주소 자원 관리 역량 국제적 인정받아</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2639&amp;page=1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10366,7 +10366,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -10377,24 +10377,24 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 10:46:37.266535+09:00</t>
+          <t>2026-09-20 12:01:47.233521+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>63051</t>
+          <t>63068</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
+          <t>대국민 혁신 정책·제안 공모전 개최</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3766&amp;page=1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -10419,7 +10419,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -10430,49 +10430,49 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-18 10:31:43.770443+09:00</t>
+          <t>2026-09-18 10:46:37.266535+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62781</t>
+          <t>63051</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
+          <t>세계경제포럼·싱가포르 사이버보안청과 인공지능(AI) 위협 대비 사이버보안 협력 강화</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2638&amp;page=1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -10480,46 +10480,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-17 17:16:36.514530+09:00</t>
+          <t>2026-09-18 10:31:43.770443+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>62507</t>
+          <t>62781</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~10월 7일(수) 16:00까지)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3765&amp;page=1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -10529,15 +10525,19 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10545,19 +10545,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-17 13:31:33.789948+09:00</t>
+          <t>2026-09-17 17:16:36.514530+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>62507</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -10567,12 +10567,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 25회차 교육생 모집(~10.10)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3764&amp;page=1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -10598,19 +10598,19 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-17 11:46:35.719751+09:00</t>
+          <t>2026-09-17 13:31:33.789948+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61484</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -10620,27 +10620,27 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 24회차 교육생 모집(~10.9)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3763&amp;page=1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
@@ -10651,19 +10651,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 09:46:37.058042+09:00</t>
+          <t>2026-09-17 11:46:35.719751+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>61111</t>
+          <t>61484</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -10673,22 +10673,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
+          <t>2026년 제13회 소프트웨어(SW) 개발보안 경진대회 개최</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3762&amp;page=1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -10699,24 +10699,24 @@
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-15 15:01:52.747371+09:00</t>
+          <t>2026-09-16 09:46:37.058042+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>61031</t>
+          <t>61111</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -10726,12 +10726,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
+          <t>민관 합동 ‘자동차 사이버 침해사고 대응 모의훈련’ 실시</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2637&amp;page=1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -10757,44 +10757,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-15 14:01:52.540884+09:00</t>
+          <t>2026-09-15 15:01:52.747371+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>57381</t>
+          <t>61031</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026 전자문서 유공 포상 공고</t>
+          <t>“새로운 보안 위협, 인공지능(AI)으로 대응” 정보보호 제품 개발 기업 대상 보안 역량 강화 교육 추진</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2636&amp;page=1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -10802,46 +10802,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-10 14:16:31.877229+09:00</t>
+          <t>2026-09-15 14:01:52.540884+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>57381</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
+          <t>2026 전자문서 유공 포상 공고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3761&amp;page=1</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -10851,7 +10847,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -10859,7 +10855,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -10867,19 +10867,19 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-10 10:46:38.794916+09:00</t>
+          <t>2026-09-10 14:16:31.877229+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>56431</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -10889,22 +10889,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
+          <t>2026년 클라우드 서비스 보안인증(CSAP) 교육 안내</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3760&amp;page=1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -10915,92 +10915,92 @@
       <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-09 12:01:35.142670+09:00</t>
+          <t>2026-09-10 10:46:38.794916+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>56969</t>
+          <t>56431</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1522</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>온마이데이터 서비스 이용 이벤트 안내</t>
+          <t>보호나라 챗봇, 국민 생활 속 정보보호 성과 인정</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2634&amp;page=1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-09 12:01:35.142670+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>54791</t>
+          <t>56969</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1522</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
+          <t>온마이데이터 서비스 이용 이벤트 안내</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3758&amp;page=1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -11010,60 +11010,60 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>402</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-07 12:01:35.243341+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>54541</t>
+          <t>54791</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
+          <t>국내 캐시 도메인이름시스템(DNS) 운영기관, 신규 암호키 반영 여부 확인하세요</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2633&amp;page=1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -11071,31 +11071,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>2026-09-07 09:01:25.516098+09:00</t>
+          <t>2026-09-07 12:01:35.243341+09:00</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>51281</t>
+          <t>54541</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -11105,27 +11101,27 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(2차, Avalanche)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3759&amp;page=1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -11140,52 +11136,56 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>2026-09-03 09:16:26.856224+09:00</t>
+          <t>2026-09-07 09:01:25.516098+09:00</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>56970</t>
+          <t>51281</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1521</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
+          <t>(행사 안내) 국외이전 제도 개선 및 CBPR 인증제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3757&amp;page=1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11193,34 +11193,34 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>2026-09-10 08:31:37.677434+09:00</t>
+          <t>2026-09-03 09:16:26.856224+09:00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>51121</t>
+          <t>56970</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1521</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
+          <t>2026 부산지역 도메인이름 분쟁해결 세미나 개최 안내(9.11)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3755&amp;page=1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -11230,7 +11230,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -11238,11 +11238,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11250,19 +11246,19 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>2026-09-02 17:31:25.610368+09:00</t>
+          <t>2026-09-10 08:31:37.677434+09:00</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>50601</t>
+          <t>51121</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11272,12 +11268,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
+          <t>2026년 블록체인 수요공급협의체(ABLE) 블록체인 수요기업(비금융분야) 모집 공고</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3754&amp;page=1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -11287,7 +11283,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -11307,44 +11303,44 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>2026-09-02 11:01:32.173328+09:00</t>
+          <t>2026-09-02 17:31:25.610368+09:00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>49872</t>
+          <t>50601</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
+          <t>2026년 9차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(9월 추천) (~9.18(금) 18시까지)</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3753&amp;page=1</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -11352,27 +11348,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>2026-09-01 12:01:47.858504+09:00</t>
+          <t>2026-09-02 11:01:32.173328+09:00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>49669</t>
+          <t>49872</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -11382,12 +11382,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
+          <t>인공지능(AI) 사이버 위협, 실전 모의훈련으로 대응</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2631&amp;page=1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -11397,35 +11397,35 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2026-09-01 09:31:38.715793+09:00</t>
+          <t>2026-09-01 12:01:47.858504+09:00</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>49631</t>
+          <t>49669</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
+          <t>「2026 위치정보 맞춤형 컨설팅 참여기업 모집」</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3752&amp;page=1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -11450,103 +11450,103 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>2026-09-01 09:01:45.980040+09:00</t>
+          <t>2026-09-01 09:31:38.715793+09:00</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>49589</t>
+          <t>49631</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1517</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
+          <t>물리보안 시스템 간 연동 장벽 낮춘다</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2632&amp;page=1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>174</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>2026-09-01 08:31:37.253592+09:00</t>
+          <t>2026-09-01 09:01:45.980040+09:00</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>48831</t>
+          <t>49589</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1517</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 23회차 교육생 모집(~9.18)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3751&amp;page=1</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -11556,35 +11556,35 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>174</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>2026-08-31 09:16:38.866405+09:00</t>
+          <t>2026-09-01 08:31:37.253592+09:00</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>46011</t>
+          <t>48831</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11594,22 +11594,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
+          <t>생성형 인공지능(AI) 기반 실전형 모의해킹 대회 개최</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2630&amp;page=1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -11625,34 +11625,34 @@
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>2026-08-27 15:01:41.552844+09:00</t>
+          <t>2026-08-31 09:16:38.866405+09:00</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>45681</t>
+          <t>46011</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
+          <t>자동차 노리는 사이버 위협, 한국인터넷진흥원-한국교통안전공단이 함께 대응한다</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2628&amp;page=1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -11670,56 +11670,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>2026-08-27 11:01:31.314899+09:00</t>
+          <t>2026-08-27 15:01:41.552844+09:00</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>45191</t>
+          <t>45681</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
+          <t>싱가포르 현지 진출 지원 국내 블록체인 기업 모집(~9.16(수) 14시)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3750&amp;page=1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -11727,42 +11723,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>2026-08-26 15:01:47.261933+09:00</t>
+          <t>2026-08-27 11:01:31.314899+09:00</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>44741</t>
+          <t>45191</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
+          <t>한국인터넷진흥원, 아·태 지역 사이버공격 대응 공동 훈련 실시</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2629&amp;page=1</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -11772,7 +11772,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -11780,56 +11780,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2026-08-26 09:31:36.427758+09:00</t>
+          <t>2026-08-26 15:01:47.261933+09:00</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>44448</t>
+          <t>44741</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
+          <t>[3차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~9/16)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3749&amp;page=1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -11837,7 +11833,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I29" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -11845,19 +11845,19 @@
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>2026-08-25 16:01:39.626193+09:00</t>
+          <t>2026-08-26 09:31:36.427758+09:00</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>43767</t>
+          <t>44448</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -11867,27 +11867,27 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
+          <t>정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 공고</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3748&amp;page=1</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
@@ -11898,19 +11898,19 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>2026-08-24 17:46:42.254577+09:00</t>
+          <t>2026-08-25 16:01:39.626193+09:00</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>43311</t>
+          <t>43767</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -11920,12 +11920,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.12)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3747&amp;page=1</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -11935,50 +11935,50 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:45.511381+09:00</t>
+          <t>2026-08-24 17:46:42.254577+09:00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>43301</t>
+          <t>43311</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
+          <t>양자내성암호 전환, 어떻게 준비해야 할까?</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2627&amp;page=1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -11988,7 +11988,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -11996,31 +11996,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>2026-08-24 12:01:36.271108+09:00</t>
+          <t>2026-08-24 12:01:45.511381+09:00</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>41161</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -12030,27 +12026,27 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
+          <t>양자내성암호 전문교육 PQC 실무과정 교육생 모집(8.24~)</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3746&amp;page=1</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -12065,34 +12061,34 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2026-08-21 16:01:38.087170+09:00</t>
+          <t>2026-08-24 12:01:36.271108+09:00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>41086</t>
+          <t>41161</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
+          <t>「블록체인 기업 맞춤형 보안 고도화 지원」 기업 모집(~8/31)</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3745&amp;page=1</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
@@ -12102,15 +12098,19 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12118,19 +12118,19 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>2026-08-21 15:01:32.139445+09:00</t>
+          <t>2026-08-21 16:01:38.087170+09:00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>34750</t>
+          <t>41086</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -12140,22 +12140,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
+          <t>2026년도 인터넷거버넌스 민간전문가 APrIGF 및 IGF 참석자 모집</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3744&amp;page=1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>59</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -12171,34 +12171,34 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>2026-08-13 17:46:21.938331+09:00</t>
+          <t>2026-08-21 15:01:32.139445+09:00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>34081</t>
+          <t>34750</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
+          <t>｢2026 블록체인 진흥주간｣ 전시부스 참가기업 모집 공고(~9.14)</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3743&amp;page=1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -12208,7 +12208,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -12216,11 +12216,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12228,44 +12224,44 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>2026-08-13 09:31:24.927741+09:00</t>
+          <t>2026-08-13 17:46:21.938331+09:00</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>34071</t>
+          <t>34081</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
+          <t>2026년 하반기 정보보호 전문서비스 기업 지정에 관한 공고</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3742&amp;page=1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>15</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -12273,42 +12269,46 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2026-08-13 09:16:35.989405+09:00</t>
+          <t>2026-08-13 09:31:24.927741+09:00</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>33789</t>
+          <t>34071</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>978</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
+          <t>"예방 넘어 대응·복구까지" 랜섬웨어 전주기 대응 방안 논의한다</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2626&amp;page=1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -12318,35 +12318,35 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>2026-08-12 16:01:25.579701+09:00</t>
+          <t>2026-08-13 09:16:35.989405+09:00</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>33749</t>
+          <t>33789</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 21회차 교육생 모집(~9.11)</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3741&amp;page=1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
@@ -12387,44 +12387,44 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>2026-08-12 15:31:25.306307+09:00</t>
+          <t>2026-08-12 16:01:25.579701+09:00</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>31741</t>
+          <t>33749</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
+          <t>2026년도 블록체인 유공 포상 계획 공고 안내(~9.21 15:00 마감)</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3740&amp;page=1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -12432,11 +12432,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12444,52 +12440,56 @@
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>2026-08-10 11:01:30.246604+09:00</t>
+          <t>2026-08-12 15:31:25.306307+09:00</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
+          <t>2026년 블록체인 수요-공급 협의체 (ABLE) 정례세미나 개최 안내(8.13.목)</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3739&amp;page=1</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>13</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I41" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -12497,19 +12497,19 @@
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>2026-08-07 17:01:29.954014+09:00</t>
+          <t>2026-08-10 11:01:30.246604+09:00</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>29728</t>
+          <t>29768</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -12519,12 +12519,12 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
+          <t>2026년 블록체인 신뢰인프라(K-BTF) 활용·확산사업 공모 사전예고</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3738&amp;page=1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -12550,19 +12550,19 @@
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2026-08-07 16:31:30.938844+09:00</t>
+          <t>2026-08-07 17:01:29.954014+09:00</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>28711</t>
+          <t>29728</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -12572,50 +12572,50 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
+          <t>2026년도 블록체인 산업 실태조사 실시 및 협조 안내</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3737&amp;page=1</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>2026-08-06 14:01:34.968573+09:00</t>
+          <t>2026-08-07 16:31:30.938844+09:00</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>27551</t>
+          <t>28711</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -12625,22 +12625,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
+          <t>한국인터넷진흥원-나주시, 고교생 개인정보·정보보호 진로 탐색 지원</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2625&amp;page=1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -12656,44 +12656,44 @@
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>2026-08-05 09:46:34.063806+09:00</t>
+          <t>2026-08-06 14:01:34.968573+09:00</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>27511</t>
+          <t>27551</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
+          <t>한국인터넷진흥원, 기업 맞춤형 사이버 위협 알림 서비스 개시</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2624&amp;page=1</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>263</t>
+          <t>101</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -12709,34 +12709,34 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>2026-08-05 09:16:33.823896+09:00</t>
+          <t>2026-08-05 09:46:34.063806+09:00</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27511</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>975</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>양자내성암호 국제 표준화 동향 분석</t>
+          <t>한국인터넷진흥원, 기관장 주도 국민 체감 성과 혁신 체계 가동</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2623&amp;page=1</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -12746,7 +12746,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -12757,24 +12757,24 @@
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>2026-08-04 16:31:26.502205+09:00</t>
+          <t>2026-08-05 09:16:33.823896+09:00</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>27128</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -12784,12 +12784,12 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
+          <t>양자내성암호 국제 표준화 동향 분석</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3736&amp;page=1</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -12799,12 +12799,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
@@ -12815,19 +12815,19 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>2026-08-04 14:46:28.764255+09:00</t>
+          <t>2026-08-04 16:31:26.502205+09:00</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>26211</t>
+          <t>27128</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -12837,50 +12837,50 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 20회차 교육생 모집(~9.4)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3735&amp;page=1</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>7</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>2026-08-03 13:31:41.722921+09:00</t>
+          <t>2026-08-04 14:46:28.764255+09:00</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>26188</t>
+          <t>26211</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -12890,12 +12890,12 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 암호모듈검증 위한 시험 전문인력 양성</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2622&amp;page=1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -12905,7 +12905,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>273</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -12916,24 +12916,24 @@
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>2026-08-03 13:16:30.325331+09:00</t>
+          <t>2026-08-03 13:31:41.722921+09:00</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>25891</t>
+          <t>26188</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
+          <t>2026년 8차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(8월 추천) (~8.21(금) 18시까지)</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3734&amp;page=1</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -12969,39 +12969,39 @@
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>2026-08-03 09:31:46.854132+09:00</t>
+          <t>2026-08-03 13:16:30.325331+09:00</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>25864</t>
+          <t>25891</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
+          <t>한국인터넷진흥원, 지역 상생 3대 사업 참여자 모집</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2621&amp;page=1</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>80</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -13019,31 +13019,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>2026-08-03 09:16:35.817723+09:00</t>
+          <t>2026-08-03 09:31:46.854132+09:00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>25863</t>
+          <t>25864</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -13053,12 +13049,12 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
+          <t>2026년 전남광주통합특별시 소상공인·사회적경제기업 판로 확대 지원기업 선발 안내(~8.14)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3730&amp;page=1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -13068,7 +13064,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -13100,7 +13096,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>25862</t>
+          <t>25863</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -13110,12 +13106,12 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
+          <t>2026년 전남광주통합특별시 지역문제 해결 프로젝트 공모전 개최 안내(~8.21)</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3731&amp;page=1</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -13125,7 +13121,7 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -13157,7 +13153,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>25861</t>
+          <t>25862</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -13167,12 +13163,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
+          <t>2026년 한국인터넷진흥원 지역공부방 참여 대학생 장학금 지원자 모집 안내(~8.28)</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3732&amp;page=1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -13182,7 +13178,7 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -13214,7 +13210,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>23221</t>
+          <t>25861</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -13224,22 +13220,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
+          <t>2026년 암호모듈 시험자 양성교육 및 필기시험 안내(8.3~8.21)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3733&amp;page=1</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -13259,52 +13255,56 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>2026-07-30 17:16:54.540202+09:00</t>
+          <t>2026-08-03 09:16:35.817723+09:00</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>22504</t>
+          <t>23221</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
+          <t>2026년 블록체인 기업성장허브 입주기업 모집(~8월 27일(목) 16:00까지)</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3729&amp;page=1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I56" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13312,19 +13312,19 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>2026-07-29 18:32:00.075123+09:00</t>
+          <t>2026-07-30 17:16:54.540202+09:00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>22464</t>
+          <t>22504</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -13334,12 +13334,12 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 19회차 교육생 모집(~8.28)</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3728&amp;page=1</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -13349,7 +13349,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -13365,19 +13365,19 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>2026-07-29 18:01:59.875668+09:00</t>
+          <t>2026-07-29 18:32:00.075123+09:00</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>20771</t>
+          <t>22464</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -13387,50 +13387,50 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
+          <t>2026년 연계정보 이용기관 안전조치 실태점검 2차 설명회 개최</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3727&amp;page=1</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>2026-07-27 17:17:05.702970+09:00</t>
+          <t>2026-07-29 18:01:59.875668+09:00</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>20191</t>
+          <t>20771</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -13440,12 +13440,12 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
+          <t>한국인터넷진흥원, 성평등가족부와 불법·유해 정보 유통 대응 맞손</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2620&amp;page=1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -13455,7 +13455,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>150</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -13471,34 +13471,34 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>2026-07-27 10:02:05.338547+09:00</t>
+          <t>2026-07-27 17:17:05.702970+09:00</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>20061</t>
+          <t>20191</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
+          <t>아피가(APIGA) 향후 10년 설계한다…전담 추진단(TF) 출범</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2619&amp;page=1</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -13508,7 +13508,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>287</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -13516,64 +13516,64 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>2026-07-27 08:31:55.019743+09:00</t>
+          <t>2026-07-27 10:02:05.338547+09:00</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>16785</t>
+          <t>20061</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
+          <t>2026년 정보보호제품 성능평가자 양성교육 신청·접수 안내(1차, BreakingPoint)</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3726&amp;page=1</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>236</t>
+          <t>246</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I61" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13581,34 +13581,34 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>2026-07-23 08:31:55.372982+09:00</t>
+          <t>2026-07-27 08:31:55.019743+09:00</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>16784</t>
+          <t>16785</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1497</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 17회차 교육생 모집(~8.7)</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3724&amp;page=1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>236</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -13646,22 +13646,22 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>16781</t>
+          <t>16784</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1497</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 18회차 교육생 모집(~8.21)</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3725&amp;page=1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -13671,7 +13671,7 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -13679,11 +13679,7 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -13703,22 +13699,22 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>16691</t>
+          <t>16781</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 16회차 교육생 모집(~7.31)</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3723&amp;page=1</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -13728,35 +13724,39 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>242</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>2026-07-22 17:32:01.526863+09:00</t>
+          <t>2026-07-23 08:31:55.372982+09:00</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>16464</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -13766,12 +13766,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
+          <t>'블록체인 기반 예금토큰 결제 인프라 확산' 사업 발대식 개최</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2618&amp;page=1</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -13781,35 +13781,35 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>278</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>2026-07-22 14:46:48.687665+09:00</t>
+          <t>2026-07-22 17:32:01.526863+09:00</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>16051</t>
+          <t>16464</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13819,12 +13819,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
+          <t>[홍보] 정보보호특성화대학 대상 사이버전문사관 제3기 후보생 모집·선발 안내</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3722&amp;page=1</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -13834,35 +13834,35 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>233</t>
+          <t>27</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>2026-07-22 09:31:50.671841+09:00</t>
+          <t>2026-07-22 14:46:48.687665+09:00</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>14611</t>
+          <t>16051</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13872,22 +13872,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
+          <t>한국인터넷진흥원, 보안 인재·글로벌 전문가 교류의 장 열어</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2617&amp;page=1</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>233</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -13903,19 +13903,19 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>2026-07-20 12:01:44.402603+09:00</t>
+          <t>2026-07-22 09:31:50.671841+09:00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -13925,12 +13925,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>아태지역 15개국 청년, 인터넷거버넌스 미래 함께 그린다</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2616&amp;page=1</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>32</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -13956,34 +13956,34 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:51.916450+09:00</t>
+          <t>2026-07-20 12:01:44.402603+09:00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>14421</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2615&amp;page=1</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>53</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -14001,56 +14001,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H69" t="inlineStr"/>
       <c r="I69" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>2026-07-20 09:46:42.059527+09:00</t>
+          <t>2026-07-20 09:46:51.916450+09:00</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>14444</t>
+          <t>14421</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1493</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
+          <t>[2차모집]2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3721&amp;page=1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -14058,7 +14054,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I70" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14066,34 +14066,34 @@
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>2026-07-20 10:01:38.608709+09:00</t>
+          <t>2026-07-20 09:46:42.059527+09:00</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11331</t>
+          <t>14444</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>1493</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 지정 공모</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3720&amp;page=1</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -14114,96 +14114,92 @@
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>2026-07-16 12:01:52.363213+09:00</t>
+          <t>2026-07-20 10:01:38.608709+09:00</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10981</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
+          <t>건설 현장 특화 폐쇄회로 텔레비전(CCTV)으로 안전 지킨다</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2614&amp;page=1</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>30</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>2026-07-15 18:01:48.663614+09:00</t>
+          <t>2026-07-16 12:01:52.363213+09:00</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10943</t>
+          <t>10981</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
+          <t>AI 기반 소스코드 취약점 점검 서비스 안내</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3719&amp;page=1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -14213,7 +14209,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>11</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -14221,7 +14217,11 @@
           <t>No</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I73" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -14229,19 +14229,19 @@
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>2026-07-15 17:31:36.060314+09:00</t>
+          <t>2026-07-15 18:01:48.663614+09:00</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10943</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -14251,12 +14251,12 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
+          <t>일상, 생활, 산업 현장 등에서 활용 가능한 위치정보 기반 안전 솔루션 모집공고</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3718&amp;page=1</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -14266,12 +14266,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
@@ -14282,19 +14282,19 @@
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>2026-07-15 14:01:31.783249+09:00</t>
+          <t>2026-07-15 17:31:36.060314+09:00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -14304,22 +14304,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
+          <t>[공지] 2026년 가명정보 전문인력 양성교육 교육생 모집 및 일정 안내</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3717&amp;page=1</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -14335,19 +14335,19 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>2026-07-14 13:31:36.337069+09:00</t>
+          <t>2026-07-15 14:01:31.783249+09:00</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>9691</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -14357,12 +14357,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
+          <t>제21회 대한민국 인터넷대상 시상계획 공고</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3716&amp;page=1</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -14372,7 +14372,7 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>12</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -14383,96 +14383,92 @@
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>2026-07-14 12:01:56.704390+09:00</t>
+          <t>2026-07-14 13:31:36.337069+09:00</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>9321</t>
+          <t>9691</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
+          <t>대한민국 국가도메인 등록 건수 반등…110만 건대 회복</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2613&amp;page=1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>42</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>2026-07-13 17:46:38.182861+09:00</t>
+          <t>2026-07-14 12:01:56.704390+09:00</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>8871</t>
+          <t>9321</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
+          <t>2026년 팀 시큐리티 코리아 기술세미나 개최 안내(7/22, 서울 로카우스 호텔)</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3715&amp;page=1</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -14482,35 +14478,39 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>9</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H78" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>2026-07-13 12:01:38.210091+09:00</t>
+          <t>2026-07-13 17:46:38.182861+09:00</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>8871</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -14520,22 +14520,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
+          <t>국민 안전 높일 제품·서비스 발굴한다…‘국민안전 위치기반서비스(LBS) 솔루션 대상’ 개최</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2612&amp;page=1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>29</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -14546,24 +14546,24 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>2026-07-10 15:31:41.134348+09:00</t>
+          <t>2026-07-13 12:01:38.210091+09:00</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>6571</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -14573,12 +14573,12 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
+          <t>공급망 보안 모델 구축 지원사업 회계감사</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3714&amp;page=1</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -14588,7 +14588,7 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -14599,24 +14599,24 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>2026-07-10 14:01:48.566995+09:00</t>
+          <t>2026-07-10 15:31:41.134348+09:00</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>5591</t>
+          <t>6571</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -14626,22 +14626,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
+          <t>“설계에서 실천으로” 기업 공급망 보안 역량 높인다</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2611&amp;page=1</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>41</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -14657,44 +14657,44 @@
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>2026-07-09 12:01:43.992717+09:00</t>
+          <t>2026-07-10 14:01:48.566995+09:00</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>5371</t>
+          <t>5591</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
+          <t>한국인터넷진흥원, 부산대 법전원과 인공지능·정보통신기술(ICT) 분쟁 해결 전문인력 양성</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2610&amp;page=1</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>33</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -14710,44 +14710,44 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>2026-07-09 09:16:53.071276+09:00</t>
+          <t>2026-07-09 12:01:43.992717+09:00</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>4762</t>
+          <t>5371</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>961</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>AI 보안 위협 대응 매뉴얼</t>
+          <t>한국인터넷진흥원, 세계은행과 제11회 글로벌 사이버보안 협력 네트워크(CAMP) 연례 회의 개최</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2609&amp;page=1</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -14755,31 +14755,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>2026-07-08 12:01:32.847380+09:00</t>
+          <t>2026-07-09 09:16:53.071276+09:00</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -14789,12 +14785,12 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>AI 보안 레드티밍 가이드</t>
+          <t>AI 보안 위협 대응 매뉴얼</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3712&amp;page=1</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -14804,7 +14800,7 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -14836,22 +14832,22 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>4251</t>
+          <t>4761</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>New</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
+          <t>AI 보안 레드티밍 가이드</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3713&amp;page=1</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -14861,7 +14857,7 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>191</t>
+          <t>3</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
@@ -14869,27 +14865,31 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>2026-07-07 15:46:43.251266+09:00</t>
+          <t>2026-07-08 12:01:32.847380+09:00</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4251</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -14899,12 +14899,12 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
+          <t>“국민 눈높이로 블록체인 서비스 살핀다” 2026년 블록체인 누리단 활동 시작</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2608&amp;page=1</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -14914,113 +14914,113 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>191</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>2026-07-07 11:01:32.170051+09:00</t>
+          <t>2026-07-07 15:46:43.251266+09:00</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>4111</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>959</t>
+          <t>New</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
+          <t>2026년 상반기 침해사고 정보공유 세미나 개최(7/22, 한국과학기술회관)</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3711&amp;page=1</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>21</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>2026-07-07 14:01:43.293075+09:00</t>
+          <t>2026-07-07 11:01:32.170051+09:00</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4111</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>959</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
+          <t>한국인터넷진흥원, 엘지유플러스와 음성스팸 대응 협력 강화</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2607&amp;page=1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>243</t>
+          <t>34</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -15028,31 +15028,27 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-07 14:01:43.293075+09:00</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -15062,12 +15058,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
+          <t>2026년 7차 정보보호 인증제품 조달청 벤처나라 추천 희망기업 모집 공고(7월 추천) (~7.24(금) 18시까지)</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3709&amp;page=1</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -15077,7 +15073,7 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -15109,32 +15105,32 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>1477</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
+          <t>2026년 '생성형 AI기반 침해대응체계 도입 및 구축' 사업 설명회(7.10, 판교 정보보호클러스터) 안내</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3710&amp;page=1</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>105</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -15142,7 +15138,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr"/>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I90" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15162,22 +15162,22 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>1478</t>
+          <t>1477</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
+          <t>국경 간 개인정보 보호 규칙 인증(CBPR) 심사기관 지정 공고</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3707&amp;page=1</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -15187,7 +15187,7 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>362</t>
+          <t>386</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -15215,22 +15215,22 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1478</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
+          <t>[접수중] 가명정보 활용 지원사업 성과공유 및 사업설명회 안내</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3708&amp;page=1</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -15240,19 +15240,15 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>522</t>
+          <t>362</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15272,7 +15268,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -15282,12 +15278,12 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>2026년 IoT 보안인증 교육과정 안내</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 15회차 교육생 모집(~7.24)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3705&amp;page=1</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -15297,7 +15293,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>652</t>
+          <t>522</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -15329,40 +15325,44 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
+          <t>2026년 IoT 보안인증 교육과정 안내</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3706&amp;page=1</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>652</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="H94" t="inlineStr"/>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I94" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15382,22 +15382,22 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
+          <t>2026년도 우수 정보보호 기술 등 지정 공고</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3704&amp;page=1</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1529</t>
+          <t>818</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -15415,11 +15415,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15439,32 +15435,32 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1270</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>1476</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
+          <t>양자내성암호 전문교육 PQC 개발·전환과정 교육생 모집(6.30~)</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3703&amp;page=1</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2264</t>
+          <t>1529</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -15472,7 +15468,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I96" t="inlineStr">
         <is>
           <t>공지사항</t>
@@ -15480,34 +15480,34 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2026-07-04 08:31:28.404468+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>1476</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
+          <t>2026 개인정보 보호·활용 기술 대상 모집 공고(~7.31(금))</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3702&amp;page=1</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -15517,7 +15517,7 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>76426</t>
+          <t>2264</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
@@ -15528,49 +15528,49 @@
       <c r="H97" t="inlineStr"/>
       <c r="I97" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-04 08:31:28.404468+09:00</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>958</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
+          <t>안전한 개인정보 활용을 위한 연구개발 본격 착수</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2605&amp;page=1</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>55906</t>
+          <t>76426</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
@@ -15598,22 +15598,22 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>957</t>
+          <t>956</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
+          <t>한국인터넷진흥원, 협력업체 상생·동반성장 간담회 개최</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2604&amp;page=1</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -15623,7 +15623,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>55329</t>
+          <t>55906</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -15651,32 +15651,32 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>955</t>
+          <t>957</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
+          <t>블록체인 관련 서울경제 보도에 대한 설명자료</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2606&amp;page=1</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>34467</t>
+          <t>55329</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -15704,22 +15704,22 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>955</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
+          <t>한국인터넷진흥원, 필리핀 사이버 위기 대응 역량 강화 지원</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2603&amp;page=1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -15729,39 +15729,35 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2945</t>
+          <t>34467</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:40.625220+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -15771,27 +15767,27 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
+          <t>「2026 블록체인 밋업데이(BCMD)」 14회차 교육생 모집(~7.17)</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3699&amp;page=1</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>2945</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -15818,32 +15814,32 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원 인사</t>
+          <t>제15회 정보보호의 날 기념식 개최 안내(서울 신라호텔, 7.8)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3697&amp;page=1</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>145255</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -15851,52 +15847,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-02 13:15:40.625220+09:00</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>953</t>
+          <t>954</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
+          <t>한국인터넷진흥원 인사</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2602&amp;page=1</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-19</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>26576</t>
+          <t>145255</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -15924,32 +15924,32 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>952</t>
+          <t>953</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
+          <t>한국인터넷진흥원, 특허법인·도메인등록기관과 케이(K)-브랜드 보호 협력</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2601&amp;page=1</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>34290</t>
+          <t>26576</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -15977,32 +15977,32 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>951</t>
+          <t>952</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
+          <t>한국인터넷진흥원, 국가 망 보안체계(N2SF) 도입 지원 본격화</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2600&amp;page=1</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>2026-06-09</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>184573</t>
+          <t>34290</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -16030,32 +16030,32 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>951</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
+          <t>아피가(APIGA) 10년 성과, 글로벌 협력 확대로 잇는다</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2599&amp;page=1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-09</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>6587</t>
+          <t>184573</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -16063,46 +16063,42 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>2026-07-20 09:31:42.552965+09:00</t>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>14403</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
+          <t>2026년 정보보호제품 성능평가 지원 공모 사업(~8/14)</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
+          <t>https://www.kisa.or.kr/401/form?postSeq=3682&amp;page=1</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -16112,7 +16108,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>51749</t>
+          <t>6587</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -16120,52 +16116,56 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>2026-07-02 13:15:50.203272+09:00</t>
+          <t>2026-07-20 09:31:42.552965+09:00</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>949</t>
+          <t>950</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+          <t>음성스팸, 유선·인터넷전화 사업자와 함께 줄인다</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2598&amp;page=1</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>78439</t>
+          <t>51749</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -16193,55 +16193,108 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>한국 정보보호 기술, 인니 통신·금융 보안 수요와 만났다</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://www.kisa.or.kr/402/form?postSeq=2597&amp;page=1</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>78439</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>2026-07-02 13:15:50.203272+09:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
           <t>38805</t>
         </is>
       </c>
-      <c r="B110" t="inlineStr">
+      <c r="B111" t="inlineStr">
         <is>
           <t>공지</t>
         </is>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C111" t="inlineStr">
         <is>
           <t>[공유] 지능형 CCTV 성능시험 재개 안내 공지</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
+      <c r="D111" t="inlineStr">
         <is>
           <t>https://www.kisa.or.kr/401/form?postSeq=3677&amp;page=1</t>
         </is>
       </c>
-      <c r="E110" t="inlineStr">
+      <c r="E111" t="inlineStr">
         <is>
           <t>2026-06-02</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F111" t="inlineStr">
         <is>
           <t>6525</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="G111" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>O</t>
         </is>
       </c>
-      <c r="I110" t="inlineStr">
+      <c r="I111" t="inlineStr">
         <is>
           <t>공지사항</t>
         </is>
       </c>
-      <c r="J110" t="inlineStr">
+      <c r="J111" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>2026-08-18 17:16:37.364015+09:00</t>
         </is>

--- a/docs/snapshot/downloads/all.xlsx
+++ b/docs/snapshot/downloads/all.xlsx
@@ -2465,7 +2465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K113"/>
+  <dimension ref="A1:K116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2528,32 +2528,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>64211</t>
+          <t>66092</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>389</t>
+          <t>388</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
+          <t>2026년도 개인정보 이노베이션 존 운영기관 예비지정 공고</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12518</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -2563,7 +2563,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -2573,44 +2573,44 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>2026-09-18 17:16:05.533385+09:00</t>
+          <t>2026-09-21 10:01:11.083915+09:00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>63321</t>
+          <t>66082</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1309</t>
+          <t>1310</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
+          <t>인공지능(AI)시대의 데이터 혁신 활용 거점 ‘개인정보 이노베이션 존’ 추가 지정</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12520</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>혁신기획담당관</t>
+          <t>데이터안전정책과</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -2630,101 +2630,101 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2026-09-17 16:30:24.744670+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>62491</t>
+          <t>66081</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>387</t>
+          <t>1311</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
+          <t>정부인사 발령(개인정보보호위원회)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12524</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>디지털소통팀</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>36</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>2026-09-16 16:16:04.999968+09:00</t>
+          <t>2026-09-21 10:00:31.705975+09:00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>386</t>
+          <t>389</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
+          <t>글로벌 AI 프라이버시 포럼 개최(9.29.)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12522</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2744,44 +2744,44 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2026-09-16 10:31:05.888883+09:00</t>
+          <t>2026-09-18 17:16:05.533385+09:00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>61982</t>
+          <t>63321</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1307</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
+          <t>「2026 개인정보 미래포럼」 제4차 전체회의 개최</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12507</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>혁신기획담당관</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2801,39 +2801,39 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-17 16:30:24.744670+09:00</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>61981</t>
+          <t>62491</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1308</t>
+          <t>387</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
+          <t>제6회 개인정보 보호의 날 기념식 개최(9.30.)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12505</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>디지털소통팀</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -2848,29 +2848,29 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>2026-09-16 10:00:24.937206+09:00</t>
+          <t>2026-09-16 16:16:04.999968+09:00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>61911</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2885,7 +2885,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12503</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>53</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -2915,44 +2915,44 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>2026-09-16 09:01:07.333518+09:00</t>
+          <t>2026-09-16 10:31:05.888883+09:00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>61982</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1305</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
+          <t>“개인정보 문의했는데 답 없거나 외국어 회신”... 개인정보위, 뤼튼·테슬라 등 5개사에 개선권고</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12499</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>사전실태점검과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2962,7 +2962,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -2972,44 +2972,44 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>2026-09-14 10:00:28.177751+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>59681</t>
+          <t>61981</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1306</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
+          <t>개인정보 보호 인증(ISMS-P) 심사 개선을 위한 개인정보 보호법 시행령 개정안 입법예고</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12500</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>국제협력담당관</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3029,54 +3029,54 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>2026-09-13 12:00:31.025848+09:00</t>
+          <t>2026-09-16 10:00:24.937206+09:00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>58591</t>
+          <t>61911</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>385</t>
+          <t>386</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
+          <t>「개인정보 보호법 시행령」 일부개정령(안) 입법예고</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12502</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>운영지원과</t>
+          <t>자율보호정책과</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -3086,54 +3086,54 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>2026-09-12 08:31:09.156431+09:00</t>
+          <t>2026-09-16 09:01:07.333518+09:00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>57981</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1304</t>
+          <t>1305</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>개인정보위, ‘구글’ 디지털성범죄 피해정보 유출 조사 신속 추진</t>
+          <t>로봇청소기 영상·음성 등 개인정보 전반적으로 안전하게 관리, 일부 미흡 사항 시정 권고</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12461</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12470</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>조사1과</t>
+          <t>사전실태점검과</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -3143,44 +3143,44 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>2026-09-11 11:15:28.934341+09:00</t>
+          <t>2026-09-14 10:00:28.177751+09:00</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>57531</t>
+          <t>59681</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>384</t>
+          <t>1306</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>개인정보 보호책임자 지정 신고 관련 주요 FAQ</t>
+          <t>개인정보 국외이전 제도 기업 설명회 개최</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12460</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12471</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>자율보호정책과</t>
+          <t>국제협력담당관</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3190,121 +3190,121 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2026-09-10 15:46:08.706294+09:00</t>
+          <t>2026-09-13 12:00:31.025848+09:00</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>57141</t>
+          <t>58591</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1303</t>
+          <t>385</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>개인정보 유출 사전예방·피해구제 강화를 위한 개인정보 보호법·시행령·고시, 9월 11일부터 시행</t>
+          <t>2026년 하반기 퇴직공무원(일반) 포상 후보자 공개검증</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS074&amp;mCode=C020010000&amp;nttId=12459</t>
+          <t>https://pipc.go.kr/np/cop/bbs/selectBoardArticle.do?bbsId=BS061&amp;mCode=C010010000&amp;nttId=12472</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>개인정보보호정책과</t>
+          <t>운영지원과</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>161</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지사항</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>2026-09-10 11:00:27.246391+09:00</t>
+          <t>2026-09-12 08:31:09.156431+09:00</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>52141</t>
+          <t>57981</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1302<